--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1143,10 +1143,10 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v>45800</v>
+        <v>34350</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
         <v>45800</v>
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1319,10 +1319,10 @@
         <v>1373979</v>
       </c>
       <c r="J19" t="n">
-        <v>5500</v>
+        <v>11000</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>11000</v>
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1757,10 +1757,10 @@
         <v>612177</v>
       </c>
       <c r="J29" t="n">
-        <v>10890</v>
+        <v>16500</v>
       </c>
       <c r="K29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>16500</v>
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1845,10 +1845,10 @@
         <v>599805</v>
       </c>
       <c r="J31" t="n">
-        <v>4510</v>
+        <v>20500</v>
       </c>
       <c r="K31" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>20500</v>
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2855,10 +2855,10 @@
         <v>434239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>36800</v>
+        <v>9570</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>36800</v>
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2987,10 +2987,10 @@
         <v>355171</v>
       </c>
       <c r="J57" t="n">
-        <v>17750</v>
+        <v>26500</v>
       </c>
       <c r="K57" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>26500</v>
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3207,10 +3207,10 @@
         <v>323198</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14070</v>
+        <v>21000</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>21000</v>
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3647,10 +3647,10 @@
         <v>475393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5270</v>
+        <v>15500</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>15500</v>
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3779,10 +3779,10 @@
         <v>327889</v>
       </c>
       <c r="J75" t="n">
-        <v>25850</v>
+        <v>47000</v>
       </c>
       <c r="K75" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>47000</v>
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3999,10 +3999,10 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36700</v>
+        <v>14680</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>36700</v>
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4175,10 +4175,10 @@
         <v>256128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>36000</v>
+        <v>9000</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>36000</v>
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4219,10 +4219,10 @@
         <v>222495</v>
       </c>
       <c r="J85" t="n">
-        <v>9600</v>
+        <v>32000</v>
       </c>
       <c r="K85" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>32000</v>
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4747,10 +4747,10 @@
         <v>330349</v>
       </c>
       <c r="J97" t="n">
-        <v>29500</v>
+        <v>59000</v>
       </c>
       <c r="K97" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>59000</v>
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-07</t>
+          <t>Steam 인기 차트 — 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -5394,33 +5394,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="G17" t="n">
-        <v>45800</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+      <c r="G17" s="4" t="n">
+        <v>34350</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -5514,33 +5514,33 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" t="n">
         <v>24580</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" t="n">
         <v>97.5</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" t="n">
         <v>1409473</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>50</v>
+      <c r="G21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5812,33 +5812,33 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>22170</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>83.8</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" t="n">
         <v>730170</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>10890</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>34</v>
+      <c r="G31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -5872,33 +5872,33 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>2892</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>95.5</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" t="n">
         <v>627791</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>4510</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>78</v>
+      <c r="G33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -6560,33 +6560,33 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="4" t="n">
         <v>11923</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="4" t="n">
         <v>493390</v>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
+      <c r="G56" s="4" t="n">
+        <v>9570</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -6650,33 +6650,33 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Project Zomboid</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Indie, RPG, Simulation, Early Access</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" t="n">
         <v>22864</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" t="n">
         <v>94.2</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" t="n">
         <v>377063</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>17750</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>33</v>
+      <c r="G59" t="n">
+        <v>26500</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6800,33 +6800,33 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Raft</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="2" t="n">
         <v>4701</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="2" t="n">
         <v>93.3</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="2" t="n">
         <v>346359</v>
       </c>
-      <c r="G64" s="4" t="n">
-        <v>14070</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>33</v>
+      <c r="G64" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7100,33 +7100,33 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="2" t="n">
         <v>30542</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="2" t="n">
         <v>95.3</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="2" t="n">
         <v>499061</v>
       </c>
-      <c r="G74" s="4" t="n">
-        <v>5270</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>66</v>
+      <c r="G74" s="2" t="n">
+        <v>15500</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7190,33 +7190,33 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" t="n">
         <v>17045</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" t="n">
         <v>370046</v>
       </c>
-      <c r="G77" s="4" t="n">
-        <v>25850</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>45</v>
+      <c r="G77" t="n">
+        <v>47000</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -7340,33 +7340,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="4" t="n">
         <v>6300</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="4" t="n">
         <v>248220</v>
       </c>
-      <c r="G82" s="2" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>0</v>
+      <c r="G82" s="4" t="n">
+        <v>14680</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="83">
@@ -7460,63 +7460,63 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Action, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="4" t="n">
         <v>7181</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" s="4" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="4" t="n">
         <v>283264</v>
       </c>
-      <c r="G86" s="2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>0</v>
+      <c r="G86" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Sons Of The Forest</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" t="n">
         <v>4450</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" t="n">
         <v>87.8</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" t="n">
         <v>253546</v>
       </c>
-      <c r="G87" s="4" t="n">
-        <v>9600</v>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>70</v>
+      <c r="G87" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7850,33 +7850,33 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" t="n">
         <v>96</v>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>DayZ</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Action, Adventure, Massively Multiplayer</t>
         </is>
       </c>
-      <c r="D99" s="4" t="n">
+      <c r="D99" t="n">
         <v>37066</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" t="n">
         <v>76.8</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" t="n">
         <v>430252</v>
       </c>
-      <c r="G99" s="4" t="n">
-        <v>29500</v>
-      </c>
-      <c r="H99" s="4" t="n">
-        <v>50</v>
+      <c r="G99" t="n">
+        <v>59000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-07</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-07</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-07</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -705,10 +705,10 @@
         <v>358266</v>
       </c>
       <c r="J5" t="n">
-        <v>22400</v>
+        <v>32000</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>32000</v>
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2415,10 +2415,10 @@
         <v>643681</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>5500</v>
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3075,10 +3075,10 @@
         <v>676667</v>
       </c>
       <c r="J59" t="n">
-        <v>18250</v>
+        <v>73000</v>
       </c>
       <c r="K59" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>73000</v>
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-08</t>
+          <t>Steam 인기 차트 — 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -5096,33 +5096,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>18028</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>380709</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>22400</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>30</v>
+      <c r="G7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6260,33 +6260,33 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Casual</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>3832</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="2" t="n">
         <v>700785</v>
       </c>
-      <c r="G46" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>40</v>
+      <c r="G46" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -6710,33 +6710,33 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Red Dead Redemption 2</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" t="n">
         <v>29885</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" t="n">
         <v>92.2</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" t="n">
         <v>733542</v>
       </c>
-      <c r="G61" s="4" t="n">
-        <v>18250</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>75</v>
+      <c r="G61" t="n">
+        <v>73000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-08</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-08</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-08</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Action, Adventure, Indie, RPG, Early Access</t>
+          <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-09</t>
+          <t>Steam 인기 차트 — 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Action, Adventure, Indie, RPG, Early Access</t>
+          <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-09</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-09</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-09</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2503,10 +2503,10 @@
         <v>272900</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21000</v>
+        <v>5250</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>21000</v>
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-10</t>
+          <t>Steam 인기 차트 — 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -6320,33 +6320,33 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="4" t="n">
         <v>8551</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="4" t="n">
         <v>295218</v>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
+      <c r="G48" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-10</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-10</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-10</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-11</t>
+          <t>Steam 인기 차트 — 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-11</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-11</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-11</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1669,10 +1669,10 @@
         <v>1071135</v>
       </c>
       <c r="J27" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" t="n">
         <v>42000</v>
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2635,10 +2635,10 @@
         <v>736611</v>
       </c>
       <c r="J49" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="K49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>21500</v>
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4263,10 +4263,10 @@
         <v>93489</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3970</v>
+        <v>26500</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>26500</v>
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-12</t>
+          <t>Steam 인기 차트 — 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5752,33 +5752,33 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>143870</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>87.2</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="4" t="n">
         <v>1227784</v>
       </c>
-      <c r="G29" t="n">
-        <v>42000</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
+      <c r="G29" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -6410,33 +6410,33 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Action, Indie, Early Access</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" t="n">
         <v>9978</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" t="n">
         <v>95.8</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" t="n">
         <v>768779</v>
       </c>
-      <c r="G51" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>30</v>
+      <c r="G51" t="n">
+        <v>21500</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -7520,33 +7520,33 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="2" t="n">
         <v>2376</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="2" t="n">
         <v>93.7</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="2" t="n">
         <v>99730</v>
       </c>
-      <c r="G88" s="4" t="n">
-        <v>3970</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>85</v>
+      <c r="G88" s="2" t="n">
+        <v>26500</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-12</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-12</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-12</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-13</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1975,10 +1975,10 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5350</v>
+        <v>10700</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>10700</v>
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-13</t>
+          <t>Steam 인기 차트 — 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -5960,33 +5960,33 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="2" t="n">
         <v>27254</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="2" t="n">
         <v>663082</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>5350</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>50</v>
+      <c r="G36" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-13</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-13</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-13</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1449,10 +1449,10 @@
         <v>736688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>66000</v>
+        <v>46200</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>66000</v>
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3119,10 +3119,10 @@
         <v>139186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>66000</v>
+        <v>6600</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>66000</v>
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3691,10 +3691,10 @@
         <v>435687</v>
       </c>
       <c r="J73" t="n">
-        <v>27400</v>
+        <v>5480</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L73" t="n">
         <v>27400</v>
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3735,10 +3735,10 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>20500</v>
+        <v>6150</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>20500</v>
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4175,10 +4175,10 @@
         <v>256128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>9000</v>
+        <v>36000</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>36000</v>
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4659,10 +4659,10 @@
         <v>177352</v>
       </c>
       <c r="J95" t="n">
-        <v>55000</v>
+        <v>5500</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L95" t="n">
         <v>55000</v>
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-14</t>
+          <t>Steam 인기 차트 — 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -5602,33 +5602,33 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Adventure, RPG, Strategy</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="4" t="n">
         <v>54771</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="4" t="n">
         <v>760662</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
+      <c r="G24" s="4" t="n">
+        <v>46200</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -6740,33 +6740,33 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Battlefield™ 2042</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Casual</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="4" t="n">
         <v>2774</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="4" t="n">
         <v>46.7</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="4" t="n">
         <v>297774</v>
       </c>
-      <c r="G62" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>0</v>
+      <c r="G62" s="4" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="63">
@@ -7130,63 +7130,63 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>4953</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="4" t="n">
         <v>95.2</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="4" t="n">
         <v>457632</v>
       </c>
-      <c r="G75" t="n">
-        <v>27400</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
+      <c r="G75" s="4" t="n">
+        <v>5480</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="4" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="4" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="4" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="2" t="n">
-        <v>20500</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>0</v>
+      <c r="G76" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="77">
@@ -7460,33 +7460,33 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Action, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="2" t="n">
         <v>7181</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="2" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="2" t="n">
         <v>283264</v>
       </c>
-      <c r="G86" s="4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>75</v>
+      <c r="G86" s="2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -7790,33 +7790,33 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Battlefield™ V</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>6327</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="4" t="n">
         <v>250288</v>
       </c>
-      <c r="G97" t="n">
-        <v>55000</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
+      <c r="G97" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="98">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-14</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-14</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-14</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-15</t>
+          <t>Steam 인기 차트 — 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-15</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-15</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-15</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-16</t>
+          <t>Steam 인기 차트 — 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-16</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-16</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-16</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-17</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4395,10 +4395,10 @@
         <v>195724</v>
       </c>
       <c r="J89" t="n">
-        <v>8000</v>
+        <v>32000</v>
       </c>
       <c r="K89" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>32000</v>
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4483,10 +4483,10 @@
         <v>304053</v>
       </c>
       <c r="J91" t="n">
-        <v>6500</v>
+        <v>65000</v>
       </c>
       <c r="K91" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>65000</v>
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-17</t>
+          <t>Steam 인기 차트 — 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -7610,33 +7610,33 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" t="n">
         <v>88</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Sid Meier's Civilization® V</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="D91" t="n">
         <v>12206</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" t="n">
         <v>95.8</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" t="n">
         <v>204265</v>
       </c>
-      <c r="G91" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>75</v>
+      <c r="G91" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7670,33 +7670,33 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" t="n">
         <v>90</v>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Sid Meier’s Civilization® VI</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="D93" t="n">
         <v>25420</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" t="n">
         <v>349920</v>
       </c>
-      <c r="G93" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="H93" s="4" t="n">
-        <v>90</v>
+      <c r="G93" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-17</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-17</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-17</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-18</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1537,10 +1537,10 @@
         <v>1122546</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5250</v>
+        <v>10500</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>10500</v>
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-18</t>
+          <t>Steam 인기 차트 — 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5662,33 +5662,33 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>18400</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="2" t="n">
         <v>1159707</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>50</v>
+      <c r="G26" s="2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-18</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-18</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-18</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-19</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-19</t>
+          <t>Steam 인기 차트 — 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-19</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-19</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-19</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-20</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4703,10 +4703,10 @@
         <v>179154</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6950</v>
+        <v>10700</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>10700</v>
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-20</t>
+          <t>Steam 인기 차트 — 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -7820,33 +7820,33 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>R.E.P.O.</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Action, Early Access</t>
         </is>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="D98" s="2" t="n">
         <v>32349</v>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="2" t="n">
         <v>96.5</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="2" t="n">
         <v>185642</v>
       </c>
-      <c r="G98" s="4" t="n">
-        <v>6950</v>
-      </c>
-      <c r="H98" s="4" t="n">
-        <v>35</v>
+      <c r="G98" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-20</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-20</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-20</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1143,10 +1143,10 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v>34350</v>
+        <v>45800</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>45800</v>
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1449,10 +1449,10 @@
         <v>736688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46200</v>
+        <v>66000</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>66000</v>
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2855,10 +2855,10 @@
         <v>434239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9570</v>
+        <v>36800</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>36800</v>
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3999,10 +3999,10 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>14680</v>
+        <v>36700</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>36700</v>
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-21</t>
+          <t>Steam 인기 차트 — 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -5394,33 +5394,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>12494</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>58.3</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" t="n">
         <v>218415</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>34350</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>25</v>
+      <c r="G17" t="n">
+        <v>45800</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5602,33 +5602,33 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Adventure, RPG, Strategy</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="2" t="n">
         <v>54771</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="2" t="n">
         <v>760662</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>46200</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>30</v>
+      <c r="G24" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6560,33 +6560,33 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="2" t="n">
         <v>11923</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="2" t="n">
         <v>493390</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>9570</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>74</v>
+      <c r="G56" s="2" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -7340,33 +7340,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="2" t="n">
         <v>6300</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="2" t="n">
         <v>248220</v>
       </c>
-      <c r="G82" s="4" t="n">
-        <v>14680</v>
-      </c>
-      <c r="H82" s="4" t="n">
-        <v>60</v>
+      <c r="G82" s="2" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-21</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-21</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-21</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-22</t>
+          <t>Steam 인기 차트 — 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-22</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-22</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-22</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-23</t>
+          <t>Steam 인기 차트 — 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-23</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-23</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-23</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-24</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -49,7 +49,7 @@
       <color rgb="00888888"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,11 +66,6 @@
         <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,14 +79,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -541,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -552,13 +546,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Counter-Strike 2</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+          <t>Counter-Strike: Global Offensive</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v/>
       </c>
       <c r="F2" s="2" t="n">
         <v>1013936</v>
@@ -573,19 +565,19 @@
         <v>7642084</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -596,13 +588,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apex Legends™</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Free To Play</t>
-        </is>
+          <t>Apex Legends</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v/>
       </c>
       <c r="F3" t="n">
         <v>124262</v>
@@ -617,19 +607,19 @@
         <v>668053</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -643,10 +633,8 @@
           <t>PUBG: BATTLEGROUNDS</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v/>
       </c>
       <c r="F4" s="2" t="n">
         <v>314682</v>
@@ -661,19 +649,19 @@
         <v>1520457</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -687,10 +675,8 @@
           <t>Palworld</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="E5" t="n">
+        <v/>
       </c>
       <c r="F5" t="n">
         <v>18028</v>
@@ -705,19 +691,19 @@
         <v>358266</v>
       </c>
       <c r="J5" t="n">
-        <v>32000</v>
+        <v/>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>32000</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -731,10 +717,8 @@
           <t>Team Fortress 2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v/>
       </c>
       <c r="F6" s="2" t="n">
         <v>43819</v>
@@ -749,19 +733,19 @@
         <v>1044264</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -772,13 +756,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Call of Duty®</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+          <t>Call of Duty: Modern Warfare II</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v/>
       </c>
       <c r="F7" t="n">
         <v>67419</v>
@@ -793,19 +775,19 @@
         <v>419594</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -863,10 +845,8 @@
           <t>Black Myth: Wukong</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="E9" t="n">
+        <v/>
       </c>
       <c r="F9" t="n">
         <v>15004</v>
@@ -881,19 +861,19 @@
         <v>1111720</v>
       </c>
       <c r="J9" t="n">
-        <v>64800</v>
+        <v/>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>64800</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +917,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -951,10 +931,8 @@
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E11" t="n">
+        <v/>
       </c>
       <c r="F11" t="n">
         <v>25122</v>
@@ -969,19 +947,19 @@
         <v>940221</v>
       </c>
       <c r="J11" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11000</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -995,10 +973,8 @@
           <t>Unturned</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual, Indie, Free To Play</t>
-        </is>
+      <c r="E12" s="2" t="n">
+        <v/>
       </c>
       <c r="F12" s="2" t="n">
         <v>10408</v>
@@ -1013,19 +989,19 @@
         <v>506516</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1043,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1081,10 +1057,8 @@
           <t>War Thunder</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Free To Play</t>
-        </is>
+      <c r="E14" s="2" t="n">
+        <v/>
       </c>
       <c r="F14" s="2" t="n">
         <v>50478</v>
@@ -1099,19 +1073,19 @@
         <v>484469</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1125,10 +1099,8 @@
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="E15" t="n">
+        <v/>
       </c>
       <c r="F15" t="n">
         <v>12494</v>
@@ -1143,19 +1115,19 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v>45800</v>
+        <v/>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>45800</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1213,10 +1185,8 @@
           <t>Warframe</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Action, RPG, Free To Play</t>
-        </is>
+      <c r="E17" t="n">
+        <v/>
       </c>
       <c r="F17" t="n">
         <v>36195</v>
@@ -1231,19 +1201,19 @@
         <v>545393</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1257,10 +1227,8 @@
           <t>ELDEN RING</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Action, RPG</t>
-        </is>
+      <c r="E18" s="2" t="n">
+        <v/>
       </c>
       <c r="F18" s="2" t="n">
         <v>29529</v>
@@ -1275,19 +1243,19 @@
         <v>981540</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>64800</v>
+        <v/>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>64800</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1301,10 +1269,8 @@
           <t>Terraria</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="E19" t="n">
+        <v/>
       </c>
       <c r="F19" t="n">
         <v>24580</v>
@@ -1319,19 +1285,19 @@
         <v>1373979</v>
       </c>
       <c r="J19" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>11000</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1339,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1387,10 +1353,8 @@
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Casual, Indie, Animation &amp; Modeling, Design &amp; Illustration, Photo Editing, Utilities</t>
-        </is>
+      <c r="E21" t="n">
+        <v/>
       </c>
       <c r="F21" t="n">
         <v>91184</v>
@@ -1405,19 +1369,19 @@
         <v>876898</v>
       </c>
       <c r="J21" t="n">
-        <v>5600</v>
+        <v/>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5600</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1431,10 +1395,8 @@
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, RPG, Strategy</t>
-        </is>
+      <c r="E22" s="2" t="n">
+        <v/>
       </c>
       <c r="F22" s="2" t="n">
         <v>54771</v>
@@ -1449,19 +1411,19 @@
         <v>736688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>66000</v>
+        <v/>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>66000</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1475,10 +1437,8 @@
           <t>Brawlhalla</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Action, Indie, Free To Play</t>
-        </is>
+      <c r="E23" t="n">
+        <v/>
       </c>
       <c r="F23" t="n">
         <v>14169</v>
@@ -1493,19 +1453,19 @@
         <v>314809</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1509,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1563,10 +1523,8 @@
           <t>Destiny 2</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Free To Play</t>
-        </is>
+      <c r="E25" t="n">
+        <v/>
       </c>
       <c r="F25" t="n">
         <v>24619</v>
@@ -1581,19 +1539,19 @@
         <v>497891</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1607,10 +1565,8 @@
           <t>Tom Clancy's Rainbow Six Siege</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="E26" s="2" t="n">
+        <v/>
       </c>
       <c r="F26" s="2" t="n">
         <v>51847</v>
@@ -1625,19 +1581,19 @@
         <v>1172854</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1651,10 +1607,8 @@
           <t>Rust</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
-        </is>
+      <c r="E27" t="n">
+        <v/>
       </c>
       <c r="F27" t="n">
         <v>143870</v>
@@ -1669,19 +1623,19 @@
         <v>1071135</v>
       </c>
       <c r="J27" t="n">
-        <v>21000</v>
+        <v/>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>42000</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1695,10 +1649,8 @@
           <t>World of Warships</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
-        </is>
+      <c r="E28" s="2" t="n">
+        <v/>
       </c>
       <c r="F28" s="2" t="n">
         <v>8518</v>
@@ -1713,19 +1665,19 @@
         <v>112887</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1739,10 +1691,8 @@
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
-        </is>
+      <c r="E29" t="n">
+        <v/>
       </c>
       <c r="F29" t="n">
         <v>22170</v>
@@ -1757,19 +1707,19 @@
         <v>612177</v>
       </c>
       <c r="J29" t="n">
-        <v>16500</v>
+        <v/>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>16500</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1783,10 +1733,8 @@
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Indie, RPG, Simulation</t>
-        </is>
+      <c r="E30" s="2" t="n">
+        <v/>
       </c>
       <c r="F30" s="2" t="n">
         <v>50662</v>
@@ -1801,19 +1749,19 @@
         <v>872384</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16000</v>
+        <v/>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>16000</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1805,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1871,10 +1819,8 @@
           <t>War Robots: Frontiers</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Action, Simulation, Free To Play</t>
-        </is>
+      <c r="E32" s="2" t="n">
+        <v/>
       </c>
       <c r="F32" s="2" t="n">
         <v>256</v>
@@ -1889,19 +1835,19 @@
         <v>1977</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1889,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1957,10 +1903,8 @@
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Action, RPG</t>
-        </is>
+      <c r="E34" s="2" t="n">
+        <v/>
       </c>
       <c r="F34" s="2" t="n">
         <v>27254</v>
@@ -1975,19 +1919,19 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10700</v>
+        <v/>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>10700</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2001,10 +1945,8 @@
           <t>Warface: Clutch</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Free To Play</t>
-        </is>
+      <c r="E35" t="n">
+        <v/>
       </c>
       <c r="F35" t="n">
         <v>270</v>
@@ -2019,19 +1961,19 @@
         <v>54554</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2017,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2089,10 +2031,8 @@
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="E37" t="n">
+        <v/>
       </c>
       <c r="F37" t="n">
         <v>5831</v>
@@ -2107,19 +2047,19 @@
         <v>88027</v>
       </c>
       <c r="J37" t="n">
-        <v>37500</v>
+        <v/>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>37500</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2177,10 +2117,8 @@
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RPG</t>
-        </is>
+      <c r="E39" t="n">
+        <v/>
       </c>
       <c r="F39" t="n">
         <v>22265</v>
@@ -2195,19 +2133,19 @@
         <v>713071</v>
       </c>
       <c r="J39" t="n">
-        <v>66000</v>
+        <v/>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>66000</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2221,10 +2159,8 @@
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E40" s="2" t="n">
+        <v/>
       </c>
       <c r="F40" s="2" t="n">
         <v>44886</v>
@@ -2239,19 +2175,19 @@
         <v>630223</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21500</v>
+        <v/>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>21500</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2265,10 +2201,8 @@
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="E41" t="n">
+        <v/>
       </c>
       <c r="F41" t="n">
         <v>5716</v>
@@ -2283,19 +2217,19 @@
         <v>289966</v>
       </c>
       <c r="J41" t="n">
-        <v>79800</v>
+        <v/>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>79800</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2309,10 +2243,8 @@
           <t>VRChat</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Casual, Massively Multiplayer, Simulation, Sports, Free To Play, Early Access</t>
-        </is>
+      <c r="E42" s="2" t="n">
+        <v/>
       </c>
       <c r="F42" s="2" t="n">
         <v>34699</v>
@@ -2327,19 +2259,19 @@
         <v>181623</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2353,10 +2285,8 @@
           <t>The Witcher 3: Wild Hunt - Complete Edition</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RPG</t>
-        </is>
+      <c r="E43" t="n">
+        <v/>
       </c>
       <c r="F43" t="n">
         <v>15893</v>
@@ -2371,19 +2301,19 @@
         <v>802993</v>
       </c>
       <c r="J43" t="n">
-        <v>54900</v>
+        <v/>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>54900</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2397,10 +2327,8 @@
           <t>Among Us</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Casual</t>
-        </is>
+      <c r="E44" s="2" t="n">
+        <v/>
       </c>
       <c r="F44" s="2" t="n">
         <v>3832</v>
@@ -2415,19 +2343,19 @@
         <v>643681</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5500</v>
+        <v/>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>5500</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2438,13 +2366,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fall Guys</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Action, Casual, Indie, Massively Multiplayer, Sports</t>
-        </is>
+          <t>Fall Guys: Ultimate Knockout</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v/>
       </c>
       <c r="F45" t="n">
         <v>664</v>
@@ -2459,19 +2385,19 @@
         <v>385154</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2485,10 +2411,8 @@
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Action, RPG</t>
-        </is>
+      <c r="E46" s="2" t="n">
+        <v/>
       </c>
       <c r="F46" s="2" t="n">
         <v>8551</v>
@@ -2503,19 +2427,19 @@
         <v>272900</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5250</v>
+        <v/>
       </c>
       <c r="K46" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>21000</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2529,10 +2453,8 @@
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Indie, Simulation</t>
-        </is>
+      <c r="E47" t="n">
+        <v/>
       </c>
       <c r="F47" t="n">
         <v>17281</v>
@@ -2547,19 +2469,19 @@
         <v>844480</v>
       </c>
       <c r="J47" t="n">
-        <v>24800</v>
+        <v/>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>24800</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2573,10 +2495,8 @@
           <t>Valheim</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="E48" s="2" t="n">
+        <v/>
       </c>
       <c r="F48" s="2" t="n">
         <v>14439</v>
@@ -2591,19 +2511,19 @@
         <v>471451</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32000</v>
+        <v/>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>32000</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2567,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2658,13 +2578,11 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Paladins®</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer, Strategy, Free To Play</t>
-        </is>
+          <t>Paladins</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v/>
       </c>
       <c r="F50" s="2" t="n">
         <v>1028</v>
@@ -2679,19 +2597,19 @@
         <v>294373</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2705,10 +2623,8 @@
           <t>NARAKA: BLADEPOINT</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
-        </is>
+      <c r="E51" t="n">
+        <v/>
       </c>
       <c r="F51" t="n">
         <v>66954</v>
@@ -2723,19 +2639,19 @@
         <v>225960</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2695,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2793,10 +2709,8 @@
           <t>Half-Life</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E53" t="n">
+        <v/>
       </c>
       <c r="F53" t="n">
         <v>634</v>
@@ -2811,19 +2725,19 @@
         <v>143086</v>
       </c>
       <c r="J53" t="n">
-        <v>10500</v>
+        <v/>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10500</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2837,10 +2751,8 @@
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E54" s="2" t="n">
+        <v/>
       </c>
       <c r="F54" s="2" t="n">
         <v>11923</v>
@@ -2855,19 +2767,19 @@
         <v>434239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>36800</v>
+        <v/>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>36800</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2881,10 +2793,8 @@
           <t>Heroes &amp; Generals</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Action, Free To Play, Indie, Massively Multiplayer, Strategy</t>
-        </is>
+      <c r="E55" t="n">
+        <v/>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2899,19 +2809,19 @@
         <v>96499</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2922,13 +2832,11 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Rocket League®</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Action, Indie, Racing, Sports</t>
-        </is>
+          <t>Rocket League</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v/>
       </c>
       <c r="F56" s="2" t="n">
         <v>21106</v>
@@ -2943,19 +2851,19 @@
         <v>509445</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2907,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +2951,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +2995,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3098,13 +3006,11 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Battlefield™ 2042</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual</t>
-        </is>
+          <t>Battlefield 2042</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v/>
       </c>
       <c r="F60" s="2" t="n">
         <v>2774</v>
@@ -3119,19 +3025,19 @@
         <v>139186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6600</v>
+        <v/>
       </c>
       <c r="K60" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>66000</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3145,10 +3051,8 @@
           <t>Halo Infinite</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="E61" t="n">
+        <v/>
       </c>
       <c r="F61" t="n">
         <v>2275</v>
@@ -3163,19 +3067,19 @@
         <v>123333</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3123,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3230,13 +3134,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SMITE®</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual, Indie, Massively Multiplayer, RPG, Simulation, Strategy, Free To Play</t>
-        </is>
+          <t>SMITE</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v/>
       </c>
       <c r="F63" t="n">
         <v>1853</v>
@@ -3251,19 +3153,19 @@
         <v>94368</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3277,10 +3179,8 @@
           <t>World of Tanks Blitz</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
-        </is>
+      <c r="E64" s="2" t="n">
+        <v/>
       </c>
       <c r="F64" s="2" t="n">
         <v>5707</v>
@@ -3295,19 +3195,19 @@
         <v>116407</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3251,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3295,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3409,10 +3309,8 @@
           <t>Schedule I</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Action, Indie, Simulation, Strategy, Early Access</t>
-        </is>
+      <c r="E67" t="n">
+        <v/>
       </c>
       <c r="F67" t="n">
         <v>22757</v>
@@ -3427,19 +3325,19 @@
         <v>200803</v>
       </c>
       <c r="J67" t="n">
-        <v>21500</v>
+        <v/>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>21500</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3453,10 +3351,8 @@
           <t>Ring of Elysium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play, Massively Multiplayer</t>
-        </is>
+      <c r="E68" s="2" t="n">
+        <v/>
       </c>
       <c r="F68" s="2" t="n">
         <v>0</v>
@@ -3471,19 +3367,19 @@
         <v>74345</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3497,10 +3393,8 @@
           <t>Portal</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E69" t="n">
+        <v/>
       </c>
       <c r="F69" t="n">
         <v>638</v>
@@ -3515,19 +3409,19 @@
         <v>175024</v>
       </c>
       <c r="J69" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>11000</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3538,13 +3432,11 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>The Sims™ 4</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Casual, Simulation, Free To Play</t>
-        </is>
+          <t>The Sims 4</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v/>
       </c>
       <c r="F70" s="2" t="n">
         <v>25276</v>
@@ -3559,19 +3451,19 @@
         <v>149064</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3585,10 +3477,8 @@
           <t>Black Squad</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="E71" t="n">
+        <v/>
       </c>
       <c r="F71" t="n">
         <v>212</v>
@@ -3603,19 +3493,19 @@
         <v>62042</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3629,10 +3519,8 @@
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
-        </is>
+      <c r="E72" s="2" t="n">
+        <v/>
       </c>
       <c r="F72" s="2" t="n">
         <v>30542</v>
@@ -3647,19 +3535,19 @@
         <v>475393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15500</v>
+        <v/>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>15500</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3673,10 +3561,8 @@
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="E73" t="n">
+        <v/>
       </c>
       <c r="F73" t="n">
         <v>4953</v>
@@ -3691,19 +3577,19 @@
         <v>435687</v>
       </c>
       <c r="J73" t="n">
-        <v>5480</v>
+        <v/>
       </c>
       <c r="K73" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>27400</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3717,10 +3603,8 @@
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Casual, Indie, Simulation</t>
-        </is>
+      <c r="E74" s="2" t="n">
+        <v/>
       </c>
       <c r="F74" s="2" t="n">
         <v>950</v>
@@ -3735,19 +3619,19 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6150</v>
+        <v/>
       </c>
       <c r="K74" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>20500</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3761,10 +3645,8 @@
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
-        </is>
+      <c r="E75" t="n">
+        <v/>
       </c>
       <c r="F75" t="n">
         <v>17045</v>
@@ -3779,19 +3661,19 @@
         <v>327889</v>
       </c>
       <c r="J75" t="n">
-        <v>47000</v>
+        <v/>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>47000</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3717,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3846,13 +3728,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>eFootball™</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Simulation, Sports, Free To Play</t>
-        </is>
+          <t>eFootball</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v/>
       </c>
       <c r="F77" t="n">
         <v>13404</v>
@@ -3867,19 +3747,19 @@
         <v>44067</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3893,10 +3773,8 @@
           <t>Street Warriors Online</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Sports</t>
-        </is>
+      <c r="E78" s="2" t="n">
+        <v/>
       </c>
       <c r="F78" s="2" t="n">
         <v>1</v>
@@ -3911,19 +3789,19 @@
         <v>941</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2200</v>
+        <v/>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2200</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3937,10 +3815,8 @@
           <t>Z1 Battle Royale</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Free To Play, Massively Multiplayer</t>
-        </is>
+      <c r="E79" t="n">
+        <v/>
       </c>
       <c r="F79" t="n">
         <v>1010</v>
@@ -3955,19 +3831,19 @@
         <v>113729</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3981,10 +3857,8 @@
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E80" s="2" t="n">
+        <v/>
       </c>
       <c r="F80" s="2" t="n">
         <v>6300</v>
@@ -3999,19 +3873,19 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36700</v>
+        <v/>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>36700</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4022,13 +3896,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sekiro™: Shadows Die Twice - GOTY Edition</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Action, Adventure</t>
-        </is>
+          <t>Sekiro: Shadows Die Twice - GOTY Edition</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v/>
       </c>
       <c r="F81" t="n">
         <v>6767</v>
@@ -4043,19 +3915,19 @@
         <v>307041</v>
       </c>
       <c r="J81" t="n">
-        <v>75000</v>
+        <v/>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>75000</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4069,10 +3941,8 @@
           <t>CyberCorp</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="E82" s="2" t="n">
+        <v/>
       </c>
       <c r="F82" s="2" t="n">
         <v>3</v>
@@ -4087,19 +3957,19 @@
         <v>266</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>16500</v>
+        <v/>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>16500</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4113,10 +3983,8 @@
           <t>Half-Life 2</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="E83" t="n">
+        <v/>
       </c>
       <c r="F83" t="n">
         <v>1555</v>
@@ -4131,19 +3999,19 @@
         <v>239721</v>
       </c>
       <c r="J83" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>11000</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4157,10 +4025,8 @@
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Action, Simulation, Strategy</t>
-        </is>
+      <c r="E84" s="2" t="n">
+        <v/>
       </c>
       <c r="F84" s="2" t="n">
         <v>7181</v>
@@ -4175,19 +4041,19 @@
         <v>256128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>36000</v>
+        <v/>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>36000</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4097,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4245,10 +4111,8 @@
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="E86" s="2" t="n">
+        <v/>
       </c>
       <c r="F86" s="2" t="n">
         <v>2376</v>
@@ -4263,19 +4127,19 @@
         <v>93489</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>26500</v>
+        <v/>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>26500</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4289,10 +4153,8 @@
           <t>Cities: Skylines</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Simulation, Strategy</t>
-        </is>
+      <c r="E87" t="n">
+        <v/>
       </c>
       <c r="F87" t="n">
         <v>8842</v>
@@ -4307,19 +4169,19 @@
         <v>256362</v>
       </c>
       <c r="J87" t="n">
-        <v>33000</v>
+        <v/>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>33000</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4333,10 +4195,8 @@
           <t>Mount &amp; Blade II: Bannerlord</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Action, Indie, RPG, Simulation, Strategy</t>
-        </is>
+      <c r="E88" s="2" t="n">
+        <v/>
       </c>
       <c r="F88" s="2" t="n">
         <v>14477</v>
@@ -4351,19 +4211,19 @@
         <v>232360</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>60000</v>
+        <v/>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>60000</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4374,13 +4234,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sid Meier's Civilization® V</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
+          <t>Sid Meier's Civilization V</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v/>
       </c>
       <c r="F89" t="n">
         <v>12206</v>
@@ -4395,19 +4253,19 @@
         <v>195724</v>
       </c>
       <c r="J89" t="n">
-        <v>32000</v>
+        <v/>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>32000</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4421,10 +4279,8 @@
           <t>Trove</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual, Massively Multiplayer, RPG, Free To Play</t>
-        </is>
+      <c r="E90" s="2" t="n">
+        <v/>
       </c>
       <c r="F90" s="2" t="n">
         <v>758</v>
@@ -4439,19 +4295,19 @@
         <v>74103</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4462,13 +4318,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sid Meier’s Civilization® VI</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
+          <t>Sid Meier’s Civilization VI</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v/>
       </c>
       <c r="F91" t="n">
         <v>25420</v>
@@ -4483,19 +4337,19 @@
         <v>304053</v>
       </c>
       <c r="J91" t="n">
-        <v>65000</v>
+        <v/>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>65000</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4509,10 +4363,8 @@
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>RPG</t>
-        </is>
+      <c r="E92" s="2" t="n">
+        <v/>
       </c>
       <c r="F92" s="2" t="n">
         <v>11179</v>
@@ -4527,19 +4379,19 @@
         <v>326054</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>22000</v>
+        <v/>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>22000</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4553,10 +4405,8 @@
           <t>Life is Strange 2</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Adventure</t>
-        </is>
+      <c r="E93" t="n">
+        <v/>
       </c>
       <c r="F93" t="n">
         <v>153</v>
@@ -4571,19 +4421,19 @@
         <v>31616</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4597,10 +4447,8 @@
           <t>Warhammer 40,000: Rogue Trader</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG, Strategy</t>
-        </is>
+      <c r="E94" s="2" t="n">
+        <v/>
       </c>
       <c r="F94" s="2" t="n">
         <v>3582</v>
@@ -4615,19 +4463,19 @@
         <v>26360</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>53000</v>
+        <v/>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>53000</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4638,13 +4486,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Battlefield™ V</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+          <t>Battlefield V</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v/>
       </c>
       <c r="F95" t="n">
         <v>6327</v>
@@ -4659,19 +4505,19 @@
         <v>177352</v>
       </c>
       <c r="J95" t="n">
-        <v>5500</v>
+        <v/>
       </c>
       <c r="K95" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>55000</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4561,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4729,10 +4575,8 @@
           <t>DayZ</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer</t>
-        </is>
+      <c r="E97" t="n">
+        <v/>
       </c>
       <c r="F97" t="n">
         <v>37066</v>
@@ -4747,19 +4591,19 @@
         <v>330349</v>
       </c>
       <c r="J97" t="n">
-        <v>59000</v>
+        <v/>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>59000</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4773,10 +4617,8 @@
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Indie, Simulation, Strategy</t>
-        </is>
+      <c r="E98" s="2" t="n">
+        <v/>
       </c>
       <c r="F98" s="2" t="n">
         <v>12596</v>
@@ -4791,19 +4633,19 @@
         <v>225479</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>42000</v>
+        <v/>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>42000</v>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4689,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4861,10 +4703,8 @@
           <t>Risk of Rain 2</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Action, Indie</t>
-        </is>
+      <c r="E100" s="2" t="n">
+        <v/>
       </c>
       <c r="F100" s="2" t="n">
         <v>7902</v>
@@ -4879,19 +4719,19 @@
         <v>293127</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>26000</v>
+        <v/>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>26000</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4902,13 +4742,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>EA SPORTS™ FIFA 23</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Simulation, Sports</t>
-        </is>
+          <t>EA SPORTS FIFA 23</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v/>
       </c>
       <c r="F101" t="n">
         <v>1280</v>
@@ -4923,13 +4761,13 @@
         <v>86192</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4959,7 +4797,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-24</t>
+          <t>Steam 인기 차트 — 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -5011,13 +4849,11 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Counter-Strike 2</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+          <t>Counter-Strike: Global Offensive</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v/>
       </c>
       <c r="D4" s="2" t="n">
         <v>1013936</v>
@@ -5029,7 +4865,7 @@
         <v>8815087</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -5041,13 +4877,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apex Legends™</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Free To Play</t>
-        </is>
+          <t>Apex Legends</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v/>
       </c>
       <c r="D5" t="n">
         <v>124262</v>
@@ -5059,7 +4893,7 @@
         <v>994979</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5074,10 +4908,8 @@
           <t>PUBG: BATTLEGROUNDS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v/>
       </c>
       <c r="D6" s="2" t="n">
         <v>314682</v>
@@ -5089,7 +4921,7 @@
         <v>2557944</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -5104,10 +4936,8 @@
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="C7" t="n">
+        <v/>
       </c>
       <c r="D7" t="n">
         <v>18028</v>
@@ -5119,7 +4949,7 @@
         <v>380709</v>
       </c>
       <c r="G7" t="n">
-        <v>32000</v>
+        <v/>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5134,10 +4964,8 @@
           <t>Team Fortress 2</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="C8" s="2" t="n">
+        <v/>
       </c>
       <c r="D8" s="2" t="n">
         <v>43819</v>
@@ -5149,7 +4977,7 @@
         <v>1161472</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -5161,13 +4989,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Call of Duty®</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+          <t>Call of Duty: Modern Warfare II</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v/>
       </c>
       <c r="D9" t="n">
         <v>67419</v>
@@ -5179,7 +5005,7 @@
         <v>714114</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5224,10 +5050,8 @@
           <t>Black Myth: Wukong</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="C11" t="n">
+        <v/>
       </c>
       <c r="D11" t="n">
         <v>15004</v>
@@ -5239,7 +5063,7 @@
         <v>1150098</v>
       </c>
       <c r="G11" t="n">
-        <v>64800</v>
+        <v/>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5284,10 +5108,8 @@
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C13" t="n">
+        <v/>
       </c>
       <c r="D13" t="n">
         <v>25122</v>
@@ -5299,7 +5121,7 @@
         <v>963983</v>
       </c>
       <c r="G13" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5314,10 +5136,8 @@
           <t>Unturned</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual, Indie, Free To Play</t>
-        </is>
+      <c r="C14" s="2" t="n">
+        <v/>
       </c>
       <c r="D14" s="2" t="n">
         <v>10408</v>
@@ -5329,7 +5149,7 @@
         <v>555368</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
@@ -5372,10 +5192,8 @@
           <t>War Thunder</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Free To Play</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v/>
       </c>
       <c r="D16" s="2" t="n">
         <v>50478</v>
@@ -5387,7 +5205,7 @@
         <v>757086</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H16" s="2" t="n">
         <v>0</v>
@@ -5402,10 +5220,8 @@
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="C17" t="n">
+        <v/>
       </c>
       <c r="D17" t="n">
         <v>12494</v>
@@ -5417,7 +5233,7 @@
         <v>218415</v>
       </c>
       <c r="G17" t="n">
-        <v>45800</v>
+        <v/>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5462,10 +5278,8 @@
           <t>Warframe</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Action, RPG, Free To Play</t>
-        </is>
+      <c r="C19" t="n">
+        <v/>
       </c>
       <c r="D19" t="n">
         <v>36195</v>
@@ -5477,7 +5291,7 @@
         <v>626503</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -5492,10 +5306,8 @@
           <t>ELDEN RING</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Action, RPG</t>
-        </is>
+      <c r="C20" s="2" t="n">
+        <v/>
       </c>
       <c r="D20" s="2" t="n">
         <v>29529</v>
@@ -5507,7 +5319,7 @@
         <v>1056677</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>64800</v>
+        <v/>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -5522,10 +5334,8 @@
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="C21" t="n">
+        <v/>
       </c>
       <c r="D21" t="n">
         <v>24580</v>
@@ -5537,7 +5347,7 @@
         <v>1409473</v>
       </c>
       <c r="G21" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -5580,10 +5390,8 @@
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Casual, Indie, Animation &amp; Modeling, Design &amp; Illustration, Photo Editing, Utilities</t>
-        </is>
+      <c r="C23" t="n">
+        <v/>
       </c>
       <c r="D23" t="n">
         <v>91184</v>
@@ -5595,7 +5403,7 @@
         <v>894458</v>
       </c>
       <c r="G23" t="n">
-        <v>5600</v>
+        <v/>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -5610,10 +5418,8 @@
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, RPG, Strategy</t>
-        </is>
+      <c r="C24" s="2" t="n">
+        <v/>
       </c>
       <c r="D24" s="2" t="n">
         <v>54771</v>
@@ -5625,7 +5431,7 @@
         <v>760662</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>66000</v>
+        <v/>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -5640,10 +5446,8 @@
           <t>Brawlhalla</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Action, Indie, Free To Play</t>
-        </is>
+      <c r="C25" t="n">
+        <v/>
       </c>
       <c r="D25" t="n">
         <v>14169</v>
@@ -5655,7 +5459,7 @@
         <v>386456</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -5700,10 +5504,8 @@
           <t>Destiny 2</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Free To Play</t>
-        </is>
+      <c r="C27" t="n">
+        <v/>
       </c>
       <c r="D27" t="n">
         <v>24619</v>
@@ -5715,7 +5517,7 @@
         <v>625616</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -5730,10 +5532,8 @@
           <t>Tom Clancy's Rainbow Six Siege</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="C28" s="2" t="n">
+        <v/>
       </c>
       <c r="D28" s="2" t="n">
         <v>51847</v>
@@ -5745,40 +5545,38 @@
         <v>1398584</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
+      <c r="C29" t="n">
+        <v/>
+      </c>
+      <c r="D29" t="n">
         <v>143870</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>87.2</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" t="n">
         <v>1227784</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>50</v>
+      <c r="G29" t="n">
+        <v/>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5790,10 +5588,8 @@
           <t>World of Warships</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
-        </is>
+      <c r="C30" s="2" t="n">
+        <v/>
       </c>
       <c r="D30" s="2" t="n">
         <v>8518</v>
@@ -5805,7 +5601,7 @@
         <v>146552</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
@@ -5820,10 +5616,8 @@
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
-        </is>
+      <c r="C31" t="n">
+        <v/>
       </c>
       <c r="D31" t="n">
         <v>22170</v>
@@ -5835,7 +5629,7 @@
         <v>730170</v>
       </c>
       <c r="G31" t="n">
-        <v>16500</v>
+        <v/>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -5850,10 +5644,8 @@
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Indie, RPG, Simulation</t>
-        </is>
+      <c r="C32" s="2" t="n">
+        <v/>
       </c>
       <c r="D32" s="2" t="n">
         <v>50662</v>
@@ -5865,7 +5657,7 @@
         <v>886195</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>16000</v>
+        <v/>
       </c>
       <c r="H32" s="2" t="n">
         <v>0</v>
@@ -5910,10 +5702,8 @@
           <t>War Robots: Frontiers</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Action, Simulation, Free To Play</t>
-        </is>
+      <c r="C34" s="2" t="n">
+        <v/>
       </c>
       <c r="D34" s="2" t="n">
         <v>256</v>
@@ -5925,7 +5715,7 @@
         <v>3082</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -5968,10 +5758,8 @@
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Action, RPG</t>
-        </is>
+      <c r="C36" s="2" t="n">
+        <v/>
       </c>
       <c r="D36" s="2" t="n">
         <v>27254</v>
@@ -5983,7 +5771,7 @@
         <v>663082</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10700</v>
+        <v/>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
@@ -5998,10 +5786,8 @@
           <t>Warface: Clutch</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Free To Play</t>
-        </is>
+      <c r="C37" t="n">
+        <v/>
       </c>
       <c r="D37" t="n">
         <v>270</v>
@@ -6013,7 +5799,7 @@
         <v>82197</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -6058,10 +5844,8 @@
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="C39" t="n">
+        <v/>
       </c>
       <c r="D39" t="n">
         <v>5831</v>
@@ -6073,7 +5857,7 @@
         <v>110623</v>
       </c>
       <c r="G39" t="n">
-        <v>37500</v>
+        <v/>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -6118,10 +5902,8 @@
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>RPG</t>
-        </is>
+      <c r="C41" t="n">
+        <v/>
       </c>
       <c r="D41" t="n">
         <v>22265</v>
@@ -6133,7 +5915,7 @@
         <v>844921</v>
       </c>
       <c r="G41" t="n">
-        <v>66000</v>
+        <v/>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -6148,10 +5930,8 @@
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C42" s="2" t="n">
+        <v/>
       </c>
       <c r="D42" s="2" t="n">
         <v>44886</v>
@@ -6163,7 +5943,7 @@
         <v>797216</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>21500</v>
+        <v/>
       </c>
       <c r="H42" s="2" t="n">
         <v>0</v>
@@ -6178,10 +5958,8 @@
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
+      <c r="C43" t="n">
+        <v/>
       </c>
       <c r="D43" t="n">
         <v>5716</v>
@@ -6193,7 +5971,7 @@
         <v>321395</v>
       </c>
       <c r="G43" t="n">
-        <v>79800</v>
+        <v/>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -6208,10 +5986,8 @@
           <t>VRChat</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Casual, Massively Multiplayer, Simulation, Sports, Free To Play, Early Access</t>
-        </is>
+      <c r="C44" s="2" t="n">
+        <v/>
       </c>
       <c r="D44" s="2" t="n">
         <v>34699</v>
@@ -6223,7 +5999,7 @@
         <v>240355</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>
@@ -6238,10 +6014,8 @@
           <t>The Witcher 3: Wild Hunt - Complete Edition</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>RPG</t>
-        </is>
+      <c r="C45" t="n">
+        <v/>
       </c>
       <c r="D45" t="n">
         <v>15893</v>
@@ -6253,7 +6027,7 @@
         <v>835349</v>
       </c>
       <c r="G45" t="n">
-        <v>54900</v>
+        <v/>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -6268,10 +6042,8 @@
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Casual</t>
-        </is>
+      <c r="C46" s="2" t="n">
+        <v/>
       </c>
       <c r="D46" s="2" t="n">
         <v>3832</v>
@@ -6283,7 +6055,7 @@
         <v>700785</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5500</v>
+        <v/>
       </c>
       <c r="H46" s="2" t="n">
         <v>0</v>
@@ -6295,13 +6067,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fall Guys</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Action, Casual, Indie, Massively Multiplayer, Sports</t>
-        </is>
+          <t>Fall Guys: Ultimate Knockout</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v/>
       </c>
       <c r="D47" t="n">
         <v>664</v>
@@ -6313,40 +6083,38 @@
         <v>473743</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Action, RPG</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="n">
+      <c r="C48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
         <v>8551</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="2" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="2" t="n">
         <v>295218</v>
       </c>
-      <c r="G48" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>75</v>
+      <c r="G48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6358,10 +6126,8 @@
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Indie, Simulation</t>
-        </is>
+      <c r="C49" t="n">
+        <v/>
       </c>
       <c r="D49" t="n">
         <v>17281</v>
@@ -6373,7 +6139,7 @@
         <v>867404</v>
       </c>
       <c r="G49" t="n">
-        <v>24800</v>
+        <v/>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -6388,10 +6154,8 @@
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="C50" s="2" t="n">
+        <v/>
       </c>
       <c r="D50" s="2" t="n">
         <v>14439</v>
@@ -6403,7 +6167,7 @@
         <v>499828</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>32000</v>
+        <v/>
       </c>
       <c r="H50" s="2" t="n">
         <v>0</v>
@@ -6445,13 +6209,11 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Paladins®</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer, Strategy, Free To Play</t>
-        </is>
+          <t>Paladins</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
       </c>
       <c r="D52" s="2" t="n">
         <v>1028</v>
@@ -6463,7 +6225,7 @@
         <v>346404</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H52" s="2" t="n">
         <v>0</v>
@@ -6478,10 +6240,8 @@
           <t>NARAKA: BLADEPOINT</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
-        </is>
+      <c r="C53" t="n">
+        <v/>
       </c>
       <c r="D53" t="n">
         <v>66954</v>
@@ -6493,7 +6253,7 @@
         <v>324927</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -6538,10 +6298,8 @@
           <t>Half-Life</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C55" t="n">
+        <v/>
       </c>
       <c r="D55" t="n">
         <v>634</v>
@@ -6553,7 +6311,7 @@
         <v>148221</v>
       </c>
       <c r="G55" t="n">
-        <v>10500</v>
+        <v/>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -6568,10 +6326,8 @@
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C56" s="2" t="n">
+        <v/>
       </c>
       <c r="D56" s="2" t="n">
         <v>11923</v>
@@ -6583,7 +6339,7 @@
         <v>493390</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>36800</v>
+        <v/>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
@@ -6598,10 +6354,8 @@
           <t>Heroes &amp; Generals</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Action, Free To Play, Indie, Massively Multiplayer, Strategy</t>
-        </is>
+      <c r="C57" t="n">
+        <v/>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -6613,7 +6367,7 @@
         <v>142763</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -6625,13 +6379,11 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Rocket League®</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Action, Indie, Racing, Sports</t>
-        </is>
+          <t>Rocket League</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v/>
       </c>
       <c r="D58" s="2" t="n">
         <v>21106</v>
@@ -6643,7 +6395,7 @@
         <v>583220</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
@@ -6740,33 +6492,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Battlefield™ 2042</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Battlefield 2042</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
         <v>2774</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="2" t="n">
         <v>46.7</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="2" t="n">
         <v>297774</v>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>90</v>
+      <c r="G62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6778,10 +6528,8 @@
           <t>Halo Infinite</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="C63" t="n">
+        <v/>
       </c>
       <c r="D63" t="n">
         <v>2275</v>
@@ -6793,7 +6541,7 @@
         <v>177041</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -6835,13 +6583,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SMITE®</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual, Indie, Massively Multiplayer, RPG, Simulation, Strategy, Free To Play</t>
-        </is>
+          <t>SMITE</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v/>
       </c>
       <c r="D65" t="n">
         <v>1853</v>
@@ -6853,7 +6599,7 @@
         <v>119796</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -6868,10 +6614,8 @@
           <t>World of Tanks Blitz</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
-        </is>
+      <c r="C66" s="2" t="n">
+        <v/>
       </c>
       <c r="D66" s="2" t="n">
         <v>5707</v>
@@ -6883,7 +6627,7 @@
         <v>148161</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H66" s="2" t="n">
         <v>0</v>
@@ -6958,10 +6702,8 @@
           <t>Schedule I</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Action, Indie, Simulation, Strategy, Early Access</t>
-        </is>
+      <c r="C69" t="n">
+        <v/>
       </c>
       <c r="D69" t="n">
         <v>22757</v>
@@ -6973,7 +6715,7 @@
         <v>204041</v>
       </c>
       <c r="G69" t="n">
-        <v>21500</v>
+        <v/>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -6988,10 +6730,8 @@
           <t>Ring of Elysium</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Action, Free To Play, Massively Multiplayer</t>
-        </is>
+      <c r="C70" s="2" t="n">
+        <v/>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
@@ -7003,7 +6743,7 @@
         <v>99837</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H70" s="2" t="n">
         <v>0</v>
@@ -7018,10 +6758,8 @@
           <t>Portal</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C71" t="n">
+        <v/>
       </c>
       <c r="D71" t="n">
         <v>638</v>
@@ -7033,7 +6771,7 @@
         <v>177741</v>
       </c>
       <c r="G71" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -7045,13 +6783,11 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>The Sims™ 4</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Casual, Simulation, Free To Play</t>
-        </is>
+          <t>The Sims 4</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
       </c>
       <c r="D72" s="2" t="n">
         <v>25276</v>
@@ -7063,7 +6799,7 @@
         <v>170727</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -7078,10 +6814,8 @@
           <t>Black Squad</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Action, Free To Play</t>
-        </is>
+      <c r="C73" t="n">
+        <v/>
       </c>
       <c r="D73" t="n">
         <v>212</v>
@@ -7093,7 +6827,7 @@
         <v>81714</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -7108,10 +6842,8 @@
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
-        </is>
+      <c r="C74" s="2" t="n">
+        <v/>
       </c>
       <c r="D74" s="2" t="n">
         <v>30542</v>
@@ -7123,70 +6855,66 @@
         <v>499061</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>15500</v>
+        <v/>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" t="n">
         <v>72</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Action, Adventure, RPG</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n">
+      <c r="C75" t="n">
+        <v/>
+      </c>
+      <c r="D75" t="n">
         <v>4953</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" t="n">
         <v>95.2</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" t="n">
         <v>457632</v>
       </c>
-      <c r="G75" s="4" t="n">
-        <v>5480</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>80</v>
+      <c r="G75" t="n">
+        <v/>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Adventure, Casual, Indie, Simulation</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n">
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="2" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="2" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>6150</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>70</v>
+      <c r="G76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -7198,10 +6926,8 @@
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
-        </is>
+      <c r="C77" t="n">
+        <v/>
       </c>
       <c r="D77" t="n">
         <v>17045</v>
@@ -7213,7 +6939,7 @@
         <v>370046</v>
       </c>
       <c r="G77" t="n">
-        <v>47000</v>
+        <v/>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -7255,13 +6981,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eFootball™</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Simulation, Sports, Free To Play</t>
-        </is>
+          <t>eFootball</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v/>
       </c>
       <c r="D79" t="n">
         <v>13404</v>
@@ -7273,7 +6997,7 @@
         <v>92333</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -7288,10 +7012,8 @@
           <t>Street Warriors Online</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Action, Massively Multiplayer, Simulation, Sports</t>
-        </is>
+      <c r="C80" s="2" t="n">
+        <v/>
       </c>
       <c r="D80" s="2" t="n">
         <v>1</v>
@@ -7303,7 +7025,7 @@
         <v>1634</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>2200</v>
+        <v/>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
@@ -7318,10 +7040,8 @@
           <t>Z1 Battle Royale</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Free To Play, Massively Multiplayer</t>
-        </is>
+      <c r="C81" t="n">
+        <v/>
       </c>
       <c r="D81" t="n">
         <v>1010</v>
@@ -7333,7 +7053,7 @@
         <v>204013</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -7348,10 +7068,8 @@
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C82" s="2" t="n">
+        <v/>
       </c>
       <c r="D82" s="2" t="n">
         <v>6300</v>
@@ -7363,7 +7081,7 @@
         <v>248220</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>36700</v>
+        <v/>
       </c>
       <c r="H82" s="2" t="n">
         <v>0</v>
@@ -7375,13 +7093,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sekiro™: Shadows Die Twice - GOTY Edition</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Action, Adventure</t>
-        </is>
+          <t>Sekiro: Shadows Die Twice - GOTY Edition</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v/>
       </c>
       <c r="D83" t="n">
         <v>6767</v>
@@ -7393,7 +7109,7 @@
         <v>322234</v>
       </c>
       <c r="G83" t="n">
-        <v>75000</v>
+        <v/>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -7408,10 +7124,8 @@
           <t>CyberCorp</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="C84" s="2" t="n">
+        <v/>
       </c>
       <c r="D84" s="2" t="n">
         <v>3</v>
@@ -7423,7 +7137,7 @@
         <v>322</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>16500</v>
+        <v/>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
@@ -7438,10 +7152,8 @@
           <t>Half-Life 2</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
+      <c r="C85" t="n">
+        <v/>
       </c>
       <c r="D85" t="n">
         <v>1555</v>
@@ -7453,7 +7165,7 @@
         <v>245627</v>
       </c>
       <c r="G85" t="n">
-        <v>11000</v>
+        <v/>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -7468,10 +7180,8 @@
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Action, Simulation, Strategy</t>
-        </is>
+      <c r="C86" s="2" t="n">
+        <v/>
       </c>
       <c r="D86" s="2" t="n">
         <v>7181</v>
@@ -7483,7 +7193,7 @@
         <v>283264</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>36000</v>
+        <v/>
       </c>
       <c r="H86" s="2" t="n">
         <v>0</v>
@@ -7528,10 +7238,8 @@
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG</t>
-        </is>
+      <c r="C88" s="2" t="n">
+        <v/>
       </c>
       <c r="D88" s="2" t="n">
         <v>2376</v>
@@ -7543,7 +7251,7 @@
         <v>99730</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>26500</v>
+        <v/>
       </c>
       <c r="H88" s="2" t="n">
         <v>0</v>
@@ -7558,10 +7266,8 @@
           <t>Cities: Skylines</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Simulation, Strategy</t>
-        </is>
+      <c r="C89" t="n">
+        <v/>
       </c>
       <c r="D89" t="n">
         <v>8842</v>
@@ -7573,7 +7279,7 @@
         <v>275770</v>
       </c>
       <c r="G89" t="n">
-        <v>33000</v>
+        <v/>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -7588,10 +7294,8 @@
           <t>Mount &amp; Blade II: Bannerlord</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Action, Indie, RPG, Simulation, Strategy</t>
-        </is>
+      <c r="C90" s="2" t="n">
+        <v/>
       </c>
       <c r="D90" s="2" t="n">
         <v>14477</v>
@@ -7603,7 +7307,7 @@
         <v>264391</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>60000</v>
+        <v/>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
@@ -7615,13 +7319,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sid Meier's Civilization® V</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
+          <t>Sid Meier's Civilization V</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v/>
       </c>
       <c r="D91" t="n">
         <v>12206</v>
@@ -7633,7 +7335,7 @@
         <v>204265</v>
       </c>
       <c r="G91" t="n">
-        <v>32000</v>
+        <v/>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -7648,10 +7350,8 @@
           <t>Trove</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Casual, Massively Multiplayer, RPG, Free To Play</t>
-        </is>
+      <c r="C92" s="2" t="n">
+        <v/>
       </c>
       <c r="D92" s="2" t="n">
         <v>758</v>
@@ -7663,7 +7363,7 @@
         <v>92370</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H92" s="2" t="n">
         <v>0</v>
@@ -7675,13 +7375,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sid Meier’s Civilization® VI</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
+          <t>Sid Meier’s Civilization VI</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v/>
       </c>
       <c r="D93" t="n">
         <v>25420</v>
@@ -7693,7 +7391,7 @@
         <v>349920</v>
       </c>
       <c r="G93" t="n">
-        <v>65000</v>
+        <v/>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -7708,10 +7406,8 @@
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>RPG</t>
-        </is>
+      <c r="C94" s="2" t="n">
+        <v/>
       </c>
       <c r="D94" s="2" t="n">
         <v>11179</v>
@@ -7723,7 +7419,7 @@
         <v>392287</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>22000</v>
+        <v/>
       </c>
       <c r="H94" s="2" t="n">
         <v>0</v>
@@ -7738,10 +7434,8 @@
           <t>Life is Strange 2</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Adventure</t>
-        </is>
+      <c r="C95" t="n">
+        <v/>
       </c>
       <c r="D95" t="n">
         <v>153</v>
@@ -7753,7 +7447,7 @@
         <v>36634</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -7768,10 +7462,8 @@
           <t>Warhammer 40,000: Rogue Trader</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Indie, RPG, Strategy</t>
-        </is>
+      <c r="C96" s="2" t="n">
+        <v/>
       </c>
       <c r="D96" s="2" t="n">
         <v>3582</v>
@@ -7783,40 +7475,38 @@
         <v>30805</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>53000</v>
+        <v/>
       </c>
       <c r="H96" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" t="n">
         <v>94</v>
       </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Battlefield™ V</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="n">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Battlefield V</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v/>
+      </c>
+      <c r="D97" t="n">
         <v>6327</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" t="n">
         <v>250288</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>90</v>
+      <c r="G97" t="n">
+        <v/>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7858,10 +7548,8 @@
           <t>DayZ</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Action, Adventure, Massively Multiplayer</t>
-        </is>
+      <c r="C99" t="n">
+        <v/>
       </c>
       <c r="D99" t="n">
         <v>37066</v>
@@ -7873,7 +7561,7 @@
         <v>430252</v>
       </c>
       <c r="G99" t="n">
-        <v>59000</v>
+        <v/>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -7888,10 +7576,8 @@
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Adventure, Indie, Simulation, Strategy</t>
-        </is>
+      <c r="C100" s="2" t="n">
+        <v/>
       </c>
       <c r="D100" s="2" t="n">
         <v>12596</v>
@@ -7903,7 +7589,7 @@
         <v>232064</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>42000</v>
+        <v/>
       </c>
       <c r="H100" s="2" t="n">
         <v>0</v>
@@ -7948,10 +7634,8 @@
           <t>Risk of Rain 2</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Action, Indie</t>
-        </is>
+      <c r="C102" s="2" t="n">
+        <v/>
       </c>
       <c r="D102" s="2" t="n">
         <v>7902</v>
@@ -7963,7 +7647,7 @@
         <v>313577</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>26000</v>
+        <v/>
       </c>
       <c r="H102" s="2" t="n">
         <v>0</v>
@@ -7975,13 +7659,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EA SPORTS™ FIFA 23</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Simulation, Sports</t>
-        </is>
+          <t>EA SPORTS FIFA 23</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v/>
       </c>
       <c r="D103" t="n">
         <v>1280</v>
@@ -7993,7 +7675,7 @@
         <v>151419</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -8029,9 +7711,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-24</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -8103,7 +7785,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>아직 7일 분량의 데이터가 쌓이지 않았습니다. 매일 자동 수집이 진행되면 이 시트가 채워집니다.</t>
         </is>
@@ -8139,9 +7821,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-24</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -8213,7 +7895,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>아직 14일 분량의 데이터가 쌓이지 않았습니다. 매일 자동 수집이 진행되면 이 시트가 채워집니다.</t>
         </is>
@@ -8249,9 +7931,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-24</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8005,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>아직 28일 분량의 데이터가 쌓이지 않았습니다. 매일 자동 수집이 진행되면 이 시트가 채워집니다.</t>
         </is>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -661,7 +661,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -745,7 +745,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -873,7 +873,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -917,7 +917,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1001,7 +1001,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1043,7 +1043,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1085,7 +1085,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1127,7 +1127,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1171,7 +1171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1213,7 +1213,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1255,7 +1255,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1297,7 +1297,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1339,7 +1339,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1381,7 +1381,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1423,7 +1423,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1465,7 +1465,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1551,7 +1551,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1593,7 +1593,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1635,7 +1635,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1677,7 +1677,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1719,7 +1719,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1761,7 +1761,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1805,7 +1805,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1847,7 +1847,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1889,7 +1889,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1931,7 +1931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1973,7 +1973,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2017,7 +2017,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2059,7 +2059,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2103,7 +2103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2145,7 +2145,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2187,7 +2187,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2229,7 +2229,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2271,7 +2271,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2313,7 +2313,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2355,7 +2355,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2397,7 +2397,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2439,7 +2439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2481,7 +2481,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2523,7 +2523,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2567,7 +2567,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2609,7 +2609,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2651,7 +2651,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2695,7 +2695,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2737,7 +2737,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2821,7 +2821,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2907,7 +2907,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2951,7 +2951,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2995,7 +2995,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3037,7 +3037,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3079,7 +3079,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3123,7 +3123,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3165,7 +3165,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3251,7 +3251,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3295,7 +3295,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3337,7 +3337,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3421,7 +3421,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3463,7 +3463,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3505,7 +3505,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3547,7 +3547,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3589,7 +3589,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3631,7 +3631,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3673,7 +3673,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3717,7 +3717,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3759,7 +3759,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3801,7 +3801,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3843,7 +3843,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3885,7 +3885,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3927,7 +3927,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3969,7 +3969,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4011,7 +4011,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4053,7 +4053,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4097,7 +4097,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4139,7 +4139,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4181,7 +4181,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4223,7 +4223,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4265,7 +4265,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4307,7 +4307,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4349,7 +4349,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4391,7 +4391,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4433,7 +4433,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4475,7 +4475,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4517,7 +4517,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4561,7 +4561,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4603,7 +4603,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4645,7 +4645,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4689,7 +4689,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4731,7 +4731,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4797,7 +4797,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-25</t>
+          <t>Steam 인기 차트 — 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-25</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-25</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-25</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-26</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -661,7 +661,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -745,7 +745,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -873,7 +873,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -917,7 +917,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1001,7 +1001,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1043,7 +1043,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1085,7 +1085,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1127,7 +1127,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1171,7 +1171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1213,7 +1213,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1255,7 +1255,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1297,7 +1297,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1339,7 +1339,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1381,7 +1381,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1423,7 +1423,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1465,7 +1465,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1551,7 +1551,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1593,7 +1593,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1635,7 +1635,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1677,7 +1677,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1719,7 +1719,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1761,7 +1761,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1805,7 +1805,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1847,7 +1847,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1889,7 +1889,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1931,7 +1931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1973,7 +1973,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2017,7 +2017,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2059,7 +2059,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2103,7 +2103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2145,7 +2145,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2187,7 +2187,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2229,7 +2229,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2271,7 +2271,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2313,7 +2313,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2355,7 +2355,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2397,7 +2397,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2439,7 +2439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2481,7 +2481,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2523,7 +2523,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2567,7 +2567,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2609,7 +2609,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2651,7 +2651,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2695,7 +2695,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2737,7 +2737,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2821,7 +2821,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2907,7 +2907,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2951,7 +2951,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2995,7 +2995,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3037,7 +3037,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3079,7 +3079,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3123,7 +3123,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3165,7 +3165,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3251,7 +3251,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3295,7 +3295,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3337,7 +3337,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3421,7 +3421,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3463,7 +3463,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3505,7 +3505,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3547,7 +3547,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3589,7 +3589,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3631,7 +3631,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3673,7 +3673,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3717,7 +3717,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3759,7 +3759,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3801,7 +3801,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3843,7 +3843,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3885,7 +3885,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3927,7 +3927,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3969,7 +3969,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4011,7 +4011,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4053,7 +4053,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4097,7 +4097,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4139,7 +4139,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4181,7 +4181,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4223,7 +4223,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4265,7 +4265,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4307,7 +4307,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4349,7 +4349,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4391,7 +4391,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4433,7 +4433,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4475,7 +4475,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4517,7 +4517,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4561,7 +4561,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4603,7 +4603,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4645,7 +4645,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4689,7 +4689,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4731,7 +4731,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4797,7 +4797,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-26</t>
+          <t>Steam 인기 차트 — 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-26</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-26</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-26</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-27</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -49,7 +49,7 @@
       <color rgb="00888888"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
         <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -79,13 +84,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -535,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -546,11 +552,13 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Counter-Strike: Global Offensive</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v/>
+          <t>Counter-Strike 2</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="F2" s="2" t="n">
         <v>1013936</v>
@@ -565,19 +573,19 @@
         <v>7642084</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -588,11 +596,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apex Legends</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v/>
+          <t>Apex Legends™</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Free To Play</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>124262</v>
@@ -607,19 +617,19 @@
         <v>668053</v>
       </c>
       <c r="J3" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -633,8 +643,10 @@
           <t>PUBG: BATTLEGROUNDS</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
+        </is>
       </c>
       <c r="F4" s="2" t="n">
         <v>314682</v>
@@ -649,19 +661,19 @@
         <v>1520457</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -675,8 +687,10 @@
           <t>Palworld</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>18028</v>
@@ -691,19 +705,19 @@
         <v>358266</v>
       </c>
       <c r="J5" t="n">
-        <v/>
+        <v>32000</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v/>
+        <v>32000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -717,8 +731,10 @@
           <t>Team Fortress 2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>43819</v>
@@ -733,19 +749,19 @@
         <v>1044264</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -756,11 +772,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Call of Duty: Modern Warfare II</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v/>
+          <t>Call of Duty®</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>67419</v>
@@ -775,19 +793,19 @@
         <v>419594</v>
       </c>
       <c r="J7" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -831,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -845,8 +863,10 @@
           <t>Black Myth: Wukong</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>15004</v>
@@ -861,19 +881,19 @@
         <v>1111720</v>
       </c>
       <c r="J9" t="n">
-        <v/>
+        <v>64800</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v/>
+        <v>64800</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -917,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -931,8 +951,10 @@
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>25122</v>
@@ -947,19 +969,19 @@
         <v>940221</v>
       </c>
       <c r="J11" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v/>
+        <v>11000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -973,8 +995,10 @@
           <t>Unturned</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual, Indie, Free To Play</t>
+        </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>10408</v>
@@ -989,19 +1013,19 @@
         <v>506516</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1043,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1057,8 +1081,10 @@
           <t>War Thunder</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Free To Play</t>
+        </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>50478</v>
@@ -1073,19 +1099,19 @@
         <v>484469</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1099,8 +1125,10 @@
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>12494</v>
@@ -1115,19 +1143,19 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v/>
+        <v>45800</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v/>
+        <v>45800</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1171,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1185,8 +1213,10 @@
           <t>Warframe</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Action, RPG, Free To Play</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>36195</v>
@@ -1201,19 +1231,19 @@
         <v>545393</v>
       </c>
       <c r="J17" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1227,8 +1257,10 @@
           <t>ELDEN RING</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Action, RPG</t>
+        </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>29529</v>
@@ -1243,19 +1275,19 @@
         <v>981540</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v/>
+        <v>64800</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v/>
+        <v>64800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1269,8 +1301,10 @@
           <t>Terraria</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>24580</v>
@@ -1285,19 +1319,19 @@
         <v>1373979</v>
       </c>
       <c r="J19" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v/>
+        <v>11000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1339,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1353,8 +1387,10 @@
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Casual, Indie, Animation &amp; Modeling, Design &amp; Illustration, Photo Editing, Utilities</t>
+        </is>
       </c>
       <c r="F21" t="n">
         <v>91184</v>
@@ -1369,19 +1405,19 @@
         <v>876898</v>
       </c>
       <c r="J21" t="n">
-        <v/>
+        <v>5600</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v/>
+        <v>5600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1395,8 +1431,10 @@
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, RPG, Strategy</t>
+        </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>54771</v>
@@ -1411,19 +1449,19 @@
         <v>736688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v/>
+        <v>66000</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v/>
+        <v>66000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1437,8 +1475,10 @@
           <t>Brawlhalla</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Action, Indie, Free To Play</t>
+        </is>
       </c>
       <c r="F23" t="n">
         <v>14169</v>
@@ -1453,19 +1493,19 @@
         <v>314809</v>
       </c>
       <c r="J23" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1509,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1523,8 +1563,10 @@
           <t>Destiny 2</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Free To Play</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>24619</v>
@@ -1539,19 +1581,19 @@
         <v>497891</v>
       </c>
       <c r="J25" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1565,8 +1607,10 @@
           <t>Tom Clancy's Rainbow Six Siege</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>51847</v>
@@ -1581,19 +1625,19 @@
         <v>1172854</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1607,8 +1651,10 @@
           <t>Rust</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>143870</v>
@@ -1623,19 +1669,19 @@
         <v>1071135</v>
       </c>
       <c r="J27" t="n">
-        <v/>
+        <v>42000</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v/>
+        <v>42000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1649,8 +1695,10 @@
           <t>World of Warships</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>8518</v>
@@ -1665,19 +1713,19 @@
         <v>112887</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1691,8 +1739,10 @@
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
+        </is>
       </c>
       <c r="F29" t="n">
         <v>22170</v>
@@ -1707,19 +1757,19 @@
         <v>612177</v>
       </c>
       <c r="J29" t="n">
-        <v/>
+        <v>16500</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v/>
+        <v>16500</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1733,8 +1783,10 @@
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
-        <v/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Indie, RPG, Simulation</t>
+        </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>50662</v>
@@ -1749,19 +1801,19 @@
         <v>872384</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v/>
+        <v>16000</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v/>
+        <v>16000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1805,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1819,8 +1871,10 @@
           <t>War Robots: Frontiers</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
-        <v/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Action, Simulation, Free To Play</t>
+        </is>
       </c>
       <c r="F32" s="2" t="n">
         <v>256</v>
@@ -1835,19 +1889,19 @@
         <v>1977</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1889,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1903,8 +1957,10 @@
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
-        <v/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Action, RPG</t>
+        </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>27254</v>
@@ -1919,19 +1975,19 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v/>
+        <v>10700</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v/>
+        <v>10700</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1945,8 +2001,10 @@
           <t>Warface: Clutch</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Free To Play</t>
+        </is>
       </c>
       <c r="F35" t="n">
         <v>270</v>
@@ -1961,19 +2019,19 @@
         <v>54554</v>
       </c>
       <c r="J35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2017,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2031,8 +2089,10 @@
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="F37" t="n">
         <v>5831</v>
@@ -2047,19 +2107,19 @@
         <v>88027</v>
       </c>
       <c r="J37" t="n">
-        <v/>
+        <v>37500</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v/>
+        <v>37500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2103,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2117,8 +2177,10 @@
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RPG</t>
+        </is>
       </c>
       <c r="F39" t="n">
         <v>22265</v>
@@ -2133,19 +2195,19 @@
         <v>713071</v>
       </c>
       <c r="J39" t="n">
-        <v/>
+        <v>66000</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v/>
+        <v>66000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2159,8 +2221,10 @@
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
-        <v/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>44886</v>
@@ -2175,19 +2239,19 @@
         <v>630223</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v/>
+        <v>21500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2201,8 +2265,10 @@
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="F41" t="n">
         <v>5716</v>
@@ -2217,19 +2283,19 @@
         <v>289966</v>
       </c>
       <c r="J41" t="n">
-        <v/>
+        <v>79800</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v/>
+        <v>79800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2243,8 +2309,10 @@
           <t>VRChat</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, Casual, Massively Multiplayer, Simulation, Sports, Free To Play, Early Access</t>
+        </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>34699</v>
@@ -2259,19 +2327,19 @@
         <v>181623</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2285,8 +2353,10 @@
           <t>The Witcher 3: Wild Hunt - Complete Edition</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RPG</t>
+        </is>
       </c>
       <c r="F43" t="n">
         <v>15893</v>
@@ -2301,19 +2371,19 @@
         <v>802993</v>
       </c>
       <c r="J43" t="n">
-        <v/>
+        <v>27450</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L43" t="n">
-        <v/>
+        <v>54900</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2327,8 +2397,10 @@
           <t>Among Us</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Casual</t>
+        </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>3832</v>
@@ -2343,19 +2415,19 @@
         <v>643681</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v/>
+        <v>5500</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v/>
+        <v>5500</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2366,11 +2438,13 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fall Guys: Ultimate Knockout</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v/>
+          <t>Fall Guys</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Action, Casual, Indie, Massively Multiplayer, Sports</t>
+        </is>
       </c>
       <c r="F45" t="n">
         <v>664</v>
@@ -2385,19 +2459,19 @@
         <v>385154</v>
       </c>
       <c r="J45" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2411,8 +2485,10 @@
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
-        <v/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Action, RPG</t>
+        </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>8551</v>
@@ -2427,19 +2503,19 @@
         <v>272900</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v/>
+        <v>6450</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v/>
+        <v>43000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2453,8 +2529,10 @@
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Indie, Simulation</t>
+        </is>
       </c>
       <c r="F47" t="n">
         <v>17281</v>
@@ -2469,19 +2547,19 @@
         <v>844480</v>
       </c>
       <c r="J47" t="n">
-        <v/>
+        <v>6200</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L47" t="n">
-        <v/>
+        <v>24800</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2495,8 +2573,10 @@
           <t>Valheim</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
-        <v/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>14439</v>
@@ -2511,19 +2591,19 @@
         <v>471451</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v/>
+        <v>32000</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v/>
+        <v>32000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2567,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2578,11 +2658,13 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Paladins</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v/>
+          <t>Paladins®</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1028</v>
@@ -2597,19 +2679,19 @@
         <v>294373</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2623,8 +2705,10 @@
           <t>NARAKA: BLADEPOINT</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
+        </is>
       </c>
       <c r="F51" t="n">
         <v>66954</v>
@@ -2639,19 +2723,19 @@
         <v>225960</v>
       </c>
       <c r="J51" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2695,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2709,8 +2793,10 @@
           <t>Half-Life</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F53" t="n">
         <v>634</v>
@@ -2725,19 +2811,19 @@
         <v>143086</v>
       </c>
       <c r="J53" t="n">
-        <v/>
+        <v>10500</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v/>
+        <v>10500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2751,8 +2837,10 @@
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
-        <v/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>11923</v>
@@ -2767,19 +2855,19 @@
         <v>434239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v/>
+        <v>36800</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v/>
+        <v>36800</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2793,8 +2881,10 @@
           <t>Heroes &amp; Generals</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Action, Free To Play, Indie, Massively Multiplayer, Strategy</t>
+        </is>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2809,19 +2899,19 @@
         <v>96499</v>
       </c>
       <c r="J55" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2832,11 +2922,13 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Rocket League</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v/>
+          <t>Rocket League®</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Action, Indie, Racing, Sports</t>
+        </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>21106</v>
@@ -2851,19 +2943,19 @@
         <v>509445</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2907,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2951,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2995,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3006,11 +3098,13 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Battlefield 2042</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v/>
+          <t>Battlefield™ 2042</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual</t>
+        </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>2774</v>
@@ -3025,19 +3119,19 @@
         <v>139186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v/>
+        <v>6600</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v/>
+        <v>66000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3051,8 +3145,10 @@
           <t>Halo Infinite</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="F61" t="n">
         <v>2275</v>
@@ -3067,19 +3163,19 @@
         <v>123333</v>
       </c>
       <c r="J61" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3123,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3134,11 +3230,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SMITE</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v/>
+          <t>SMITE®</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual, Indie, Massively Multiplayer, RPG, Simulation, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="F63" t="n">
         <v>1853</v>
@@ -3153,19 +3251,19 @@
         <v>94368</v>
       </c>
       <c r="J63" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3179,8 +3277,10 @@
           <t>World of Tanks Blitz</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
-        <v/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>5707</v>
@@ -3195,19 +3295,19 @@
         <v>116407</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3251,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3295,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3309,8 +3409,10 @@
           <t>Schedule I</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Action, Indie, Simulation, Strategy, Early Access</t>
+        </is>
       </c>
       <c r="F67" t="n">
         <v>22757</v>
@@ -3325,19 +3427,19 @@
         <v>200803</v>
       </c>
       <c r="J67" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v/>
+        <v>21500</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3351,8 +3453,10 @@
           <t>Ring of Elysium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
-        <v/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play, Massively Multiplayer</t>
+        </is>
       </c>
       <c r="F68" s="2" t="n">
         <v>0</v>
@@ -3367,19 +3471,19 @@
         <v>74345</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3393,8 +3497,10 @@
           <t>Portal</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F69" t="n">
         <v>638</v>
@@ -3409,19 +3515,19 @@
         <v>175024</v>
       </c>
       <c r="J69" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v/>
+        <v>11000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3432,11 +3538,13 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>The Sims 4</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v/>
+          <t>The Sims™ 4</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, Casual, Simulation, Free To Play</t>
+        </is>
       </c>
       <c r="F70" s="2" t="n">
         <v>25276</v>
@@ -3451,19 +3559,19 @@
         <v>149064</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3477,8 +3585,10 @@
           <t>Black Squad</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="F71" t="n">
         <v>212</v>
@@ -3493,19 +3603,19 @@
         <v>62042</v>
       </c>
       <c r="J71" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3519,8 +3629,10 @@
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
-        <v/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="F72" s="2" t="n">
         <v>30542</v>
@@ -3535,19 +3647,19 @@
         <v>475393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v/>
+        <v>15500</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v/>
+        <v>15500</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3561,8 +3673,10 @@
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="F73" t="n">
         <v>4953</v>
@@ -3577,19 +3691,19 @@
         <v>435687</v>
       </c>
       <c r="J73" t="n">
-        <v/>
+        <v>27400</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v/>
+        <v>27400</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3603,8 +3717,10 @@
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
-        <v/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, Casual, Indie, Simulation</t>
+        </is>
       </c>
       <c r="F74" s="2" t="n">
         <v>950</v>
@@ -3619,19 +3735,19 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v/>
+        <v>6150</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v/>
+        <v>20500</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3645,8 +3761,10 @@
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="F75" t="n">
         <v>17045</v>
@@ -3661,19 +3779,19 @@
         <v>327889</v>
       </c>
       <c r="J75" t="n">
-        <v/>
+        <v>47000</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v/>
+        <v>47000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3717,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3728,11 +3846,13 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>eFootball</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v/>
+          <t>eFootball™</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Simulation, Sports, Free To Play</t>
+        </is>
       </c>
       <c r="F77" t="n">
         <v>13404</v>
@@ -3747,19 +3867,19 @@
         <v>44067</v>
       </c>
       <c r="J77" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3773,8 +3893,10 @@
           <t>Street Warriors Online</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
-        <v/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Sports</t>
+        </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>1</v>
@@ -3789,19 +3911,19 @@
         <v>941</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v/>
+        <v>2200</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v/>
+        <v>2200</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3815,8 +3937,10 @@
           <t>Z1 Battle Royale</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Free To Play, Massively Multiplayer</t>
+        </is>
       </c>
       <c r="F79" t="n">
         <v>1010</v>
@@ -3831,19 +3955,19 @@
         <v>113729</v>
       </c>
       <c r="J79" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3857,8 +3981,10 @@
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
-        <v/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>6300</v>
@@ -3873,19 +3999,19 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v/>
+        <v>36700</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v/>
+        <v>36700</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3896,11 +4022,13 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sekiro: Shadows Die Twice - GOTY Edition</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v/>
+          <t>Sekiro™: Shadows Die Twice - GOTY Edition</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Action, Adventure</t>
+        </is>
       </c>
       <c r="F81" t="n">
         <v>6767</v>
@@ -3915,19 +4043,19 @@
         <v>307041</v>
       </c>
       <c r="J81" t="n">
-        <v/>
+        <v>75000</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v/>
+        <v>75000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3941,8 +4069,10 @@
           <t>CyberCorp</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
-        <v/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="F82" s="2" t="n">
         <v>3</v>
@@ -3957,19 +4087,19 @@
         <v>266</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v/>
+        <v>16500</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v/>
+        <v>16500</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3983,8 +4113,10 @@
           <t>Half-Life 2</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F83" t="n">
         <v>1555</v>
@@ -3999,19 +4131,19 @@
         <v>239721</v>
       </c>
       <c r="J83" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v/>
+        <v>11000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4025,8 +4157,10 @@
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
-        <v/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Action, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>7181</v>
@@ -4041,19 +4175,19 @@
         <v>256128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v/>
+        <v>36000</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v/>
+        <v>36000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4097,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4111,8 +4245,10 @@
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
-        <v/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="F86" s="2" t="n">
         <v>2376</v>
@@ -4127,19 +4263,19 @@
         <v>93489</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v/>
+        <v>26500</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v/>
+        <v>26500</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4153,8 +4289,10 @@
           <t>Cities: Skylines</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Simulation, Strategy</t>
+        </is>
       </c>
       <c r="F87" t="n">
         <v>8842</v>
@@ -4169,19 +4307,19 @@
         <v>256362</v>
       </c>
       <c r="J87" t="n">
-        <v/>
+        <v>33000</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v/>
+        <v>33000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4195,8 +4333,10 @@
           <t>Mount &amp; Blade II: Bannerlord</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n">
-        <v/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Action, Indie, RPG, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>14477</v>
@@ -4211,19 +4351,19 @@
         <v>232360</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v/>
+        <v>60000</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v/>
+        <v>60000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4234,11 +4374,13 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sid Meier's Civilization V</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v/>
+          <t>Sid Meier's Civilization® V</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
       </c>
       <c r="F89" t="n">
         <v>12206</v>
@@ -4253,19 +4395,19 @@
         <v>195724</v>
       </c>
       <c r="J89" t="n">
-        <v/>
+        <v>32000</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v/>
+        <v>32000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4279,8 +4421,10 @@
           <t>Trove</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
-        <v/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual, Massively Multiplayer, RPG, Free To Play</t>
+        </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>758</v>
@@ -4295,19 +4439,19 @@
         <v>74103</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4318,11 +4462,13 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sid Meier’s Civilization VI</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v/>
+          <t>Sid Meier’s Civilization® VI</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
       </c>
       <c r="F91" t="n">
         <v>25420</v>
@@ -4337,19 +4483,19 @@
         <v>304053</v>
       </c>
       <c r="J91" t="n">
-        <v/>
+        <v>65000</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v/>
+        <v>65000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4363,8 +4509,10 @@
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n">
-        <v/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>RPG</t>
+        </is>
       </c>
       <c r="F92" s="2" t="n">
         <v>11179</v>
@@ -4379,19 +4527,19 @@
         <v>326054</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v/>
+        <v>22000</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v/>
+        <v>22000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4405,8 +4553,10 @@
           <t>Life is Strange 2</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
       </c>
       <c r="F93" t="n">
         <v>153</v>
@@ -4421,19 +4571,19 @@
         <v>31616</v>
       </c>
       <c r="J93" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4447,8 +4597,10 @@
           <t>Warhammer 40,000: Rogue Trader</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n">
-        <v/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG, Strategy</t>
+        </is>
       </c>
       <c r="F94" s="2" t="n">
         <v>3582</v>
@@ -4463,19 +4615,19 @@
         <v>26360</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v/>
+        <v>15900</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v/>
+        <v>53000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4486,11 +4638,13 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Battlefield V</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v/>
+          <t>Battlefield™ V</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="F95" t="n">
         <v>6327</v>
@@ -4505,19 +4659,19 @@
         <v>177352</v>
       </c>
       <c r="J95" t="n">
-        <v/>
+        <v>5500</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L95" t="n">
-        <v/>
+        <v>55000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4561,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4575,8 +4729,10 @@
           <t>DayZ</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer</t>
+        </is>
       </c>
       <c r="F97" t="n">
         <v>37066</v>
@@ -4591,19 +4747,19 @@
         <v>330349</v>
       </c>
       <c r="J97" t="n">
-        <v/>
+        <v>59000</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v/>
+        <v>59000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4617,8 +4773,10 @@
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n">
-        <v/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, Indie, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="F98" s="2" t="n">
         <v>12596</v>
@@ -4633,19 +4791,19 @@
         <v>225479</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v/>
+        <v>29400</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v/>
+        <v>42000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4689,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4703,8 +4861,10 @@
           <t>Risk of Rain 2</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
-        <v/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Action, Indie</t>
+        </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>7902</v>
@@ -4719,19 +4879,19 @@
         <v>293127</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v/>
+        <v>26000</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v/>
+        <v>26000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4742,11 +4902,13 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>EA SPORTS FIFA 23</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v/>
+          <t>EA SPORTS™ FIFA 23</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Simulation, Sports</t>
+        </is>
       </c>
       <c r="F101" t="n">
         <v>1280</v>
@@ -4761,13 +4923,13 @@
         <v>86192</v>
       </c>
       <c r="J101" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4797,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-27</t>
+          <t>Steam 인기 차트 — 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4849,11 +5011,13 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Counter-Strike: Global Offensive</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v/>
+          <t>Counter-Strike 2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>1013936</v>
@@ -4865,7 +5029,7 @@
         <v>8815087</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -4877,11 +5041,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apex Legends</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v/>
+          <t>Apex Legends™</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Free To Play</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>124262</v>
@@ -4893,7 +5059,7 @@
         <v>994979</v>
       </c>
       <c r="G5" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4908,8 +5074,10 @@
           <t>PUBG: BATTLEGROUNDS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
+        </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>314682</v>
@@ -4921,7 +5089,7 @@
         <v>2557944</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -4936,8 +5104,10 @@
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="D7" t="n">
         <v>18028</v>
@@ -4949,7 +5119,7 @@
         <v>380709</v>
       </c>
       <c r="G7" t="n">
-        <v/>
+        <v>32000</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4964,8 +5134,10 @@
           <t>Team Fortress 2</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>43819</v>
@@ -4977,7 +5149,7 @@
         <v>1161472</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -4989,11 +5161,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Call of Duty: Modern Warfare II</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v/>
+          <t>Call of Duty®</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>67419</v>
@@ -5005,7 +5179,7 @@
         <v>714114</v>
       </c>
       <c r="G9" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5050,8 +5224,10 @@
           <t>Black Myth: Wukong</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="D11" t="n">
         <v>15004</v>
@@ -5063,7 +5239,7 @@
         <v>1150098</v>
       </c>
       <c r="G11" t="n">
-        <v/>
+        <v>64800</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5108,8 +5284,10 @@
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D13" t="n">
         <v>25122</v>
@@ -5121,7 +5299,7 @@
         <v>963983</v>
       </c>
       <c r="G13" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5136,8 +5314,10 @@
           <t>Unturned</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual, Indie, Free To Play</t>
+        </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>10408</v>
@@ -5149,7 +5329,7 @@
         <v>555368</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
@@ -5192,8 +5372,10 @@
           <t>War Thunder</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Free To Play</t>
+        </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>50478</v>
@@ -5205,7 +5387,7 @@
         <v>757086</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>0</v>
@@ -5220,8 +5402,10 @@
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="D17" t="n">
         <v>12494</v>
@@ -5233,7 +5417,7 @@
         <v>218415</v>
       </c>
       <c r="G17" t="n">
-        <v/>
+        <v>45800</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5278,8 +5462,10 @@
           <t>Warframe</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Action, RPG, Free To Play</t>
+        </is>
       </c>
       <c r="D19" t="n">
         <v>36195</v>
@@ -5291,7 +5477,7 @@
         <v>626503</v>
       </c>
       <c r="G19" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -5306,8 +5492,10 @@
           <t>ELDEN RING</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Action, RPG</t>
+        </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>29529</v>
@@ -5319,7 +5507,7 @@
         <v>1056677</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v/>
+        <v>64800</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -5334,8 +5522,10 @@
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="D21" t="n">
         <v>24580</v>
@@ -5347,7 +5537,7 @@
         <v>1409473</v>
       </c>
       <c r="G21" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -5390,8 +5580,10 @@
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Casual, Indie, Animation &amp; Modeling, Design &amp; Illustration, Photo Editing, Utilities</t>
+        </is>
       </c>
       <c r="D23" t="n">
         <v>91184</v>
@@ -5403,7 +5595,7 @@
         <v>894458</v>
       </c>
       <c r="G23" t="n">
-        <v/>
+        <v>5600</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -5418,8 +5610,10 @@
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, RPG, Strategy</t>
+        </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>54771</v>
@@ -5431,7 +5625,7 @@
         <v>760662</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v/>
+        <v>66000</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -5446,8 +5640,10 @@
           <t>Brawlhalla</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Action, Indie, Free To Play</t>
+        </is>
       </c>
       <c r="D25" t="n">
         <v>14169</v>
@@ -5459,7 +5655,7 @@
         <v>386456</v>
       </c>
       <c r="G25" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -5504,8 +5700,10 @@
           <t>Destiny 2</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Free To Play</t>
+        </is>
       </c>
       <c r="D27" t="n">
         <v>24619</v>
@@ -5517,7 +5715,7 @@
         <v>625616</v>
       </c>
       <c r="G27" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -5532,8 +5730,10 @@
           <t>Tom Clancy's Rainbow Six Siege</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>51847</v>
@@ -5545,7 +5745,7 @@
         <v>1398584</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>
@@ -5560,8 +5760,10 @@
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
+        </is>
       </c>
       <c r="D29" t="n">
         <v>143870</v>
@@ -5573,7 +5775,7 @@
         <v>1227784</v>
       </c>
       <c r="G29" t="n">
-        <v/>
+        <v>42000</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -5588,8 +5790,10 @@
           <t>World of Warships</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>8518</v>
@@ -5601,7 +5805,7 @@
         <v>146552</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
@@ -5616,8 +5820,10 @@
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
+        </is>
       </c>
       <c r="D31" t="n">
         <v>22170</v>
@@ -5629,7 +5835,7 @@
         <v>730170</v>
       </c>
       <c r="G31" t="n">
-        <v/>
+        <v>16500</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -5644,8 +5850,10 @@
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Indie, RPG, Simulation</t>
+        </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>50662</v>
@@ -5657,7 +5865,7 @@
         <v>886195</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v/>
+        <v>16000</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>0</v>
@@ -5702,8 +5910,10 @@
           <t>War Robots: Frontiers</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Action, Simulation, Free To Play</t>
+        </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>256</v>
@@ -5715,7 +5925,7 @@
         <v>3082</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -5758,8 +5968,10 @@
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Action, RPG</t>
+        </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>27254</v>
@@ -5771,7 +5983,7 @@
         <v>663082</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v/>
+        <v>10700</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
@@ -5786,8 +5998,10 @@
           <t>Warface: Clutch</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Free To Play</t>
+        </is>
       </c>
       <c r="D37" t="n">
         <v>270</v>
@@ -5799,7 +6013,7 @@
         <v>82197</v>
       </c>
       <c r="G37" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -5844,8 +6058,10 @@
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="D39" t="n">
         <v>5831</v>
@@ -5857,7 +6073,7 @@
         <v>110623</v>
       </c>
       <c r="G39" t="n">
-        <v/>
+        <v>37500</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -5902,8 +6118,10 @@
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RPG</t>
+        </is>
       </c>
       <c r="D41" t="n">
         <v>22265</v>
@@ -5915,7 +6133,7 @@
         <v>844921</v>
       </c>
       <c r="G41" t="n">
-        <v/>
+        <v>66000</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -5930,8 +6148,10 @@
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D42" s="2" t="n">
         <v>44886</v>
@@ -5943,7 +6163,7 @@
         <v>797216</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>0</v>
@@ -5958,8 +6178,10 @@
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="D43" t="n">
         <v>5716</v>
@@ -5971,7 +6193,7 @@
         <v>321395</v>
       </c>
       <c r="G43" t="n">
-        <v/>
+        <v>79800</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5986,8 +6208,10 @@
           <t>VRChat</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, Casual, Massively Multiplayer, Simulation, Sports, Free To Play, Early Access</t>
+        </is>
       </c>
       <c r="D44" s="2" t="n">
         <v>34699</v>
@@ -5999,38 +6223,40 @@
         <v>240355</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt - Complete Edition</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v/>
-      </c>
-      <c r="D45" t="n">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>RPG</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>15893</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="4" t="n">
         <v>835349</v>
       </c>
-      <c r="G45" t="n">
-        <v/>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
+      <c r="G45" s="4" t="n">
+        <v>27450</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -6042,8 +6268,10 @@
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Casual</t>
+        </is>
       </c>
       <c r="D46" s="2" t="n">
         <v>3832</v>
@@ -6055,7 +6283,7 @@
         <v>700785</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v/>
+        <v>5500</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>0</v>
@@ -6067,11 +6295,13 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fall Guys: Ultimate Knockout</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v/>
+          <t>Fall Guys</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Action, Casual, Indie, Massively Multiplayer, Sports</t>
+        </is>
       </c>
       <c r="D47" t="n">
         <v>664</v>
@@ -6083,66 +6313,70 @@
         <v>473743</v>
       </c>
       <c r="G47" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D48" s="2" t="n">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Action, RPG</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
         <v>8551</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="4" t="n">
         <v>295218</v>
       </c>
-      <c r="G48" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
+      <c r="G48" s="4" t="n">
+        <v>6450</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v/>
-      </c>
-      <c r="D49" t="n">
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Indie, Simulation</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
         <v>17281</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="4" t="n">
         <v>867404</v>
       </c>
-      <c r="G49" t="n">
-        <v/>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
+      <c r="G49" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="50">
@@ -6154,8 +6388,10 @@
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="D50" s="2" t="n">
         <v>14439</v>
@@ -6167,7 +6403,7 @@
         <v>499828</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v/>
+        <v>32000</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>0</v>
@@ -6209,11 +6445,13 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Paladins</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v/>
+          <t>Paladins®</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="D52" s="2" t="n">
         <v>1028</v>
@@ -6225,7 +6463,7 @@
         <v>346404</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0</v>
@@ -6240,8 +6478,10 @@
           <t>NARAKA: BLADEPOINT</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer, Free To Play</t>
+        </is>
       </c>
       <c r="D53" t="n">
         <v>66954</v>
@@ -6253,7 +6493,7 @@
         <v>324927</v>
       </c>
       <c r="G53" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -6298,8 +6538,10 @@
           <t>Half-Life</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D55" t="n">
         <v>634</v>
@@ -6311,7 +6553,7 @@
         <v>148221</v>
       </c>
       <c r="G55" t="n">
-        <v/>
+        <v>10500</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -6326,8 +6568,10 @@
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D56" s="2" t="n">
         <v>11923</v>
@@ -6339,7 +6583,7 @@
         <v>493390</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v/>
+        <v>36800</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
@@ -6354,8 +6598,10 @@
           <t>Heroes &amp; Generals</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Action, Free To Play, Indie, Massively Multiplayer, Strategy</t>
+        </is>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -6367,7 +6613,7 @@
         <v>142763</v>
       </c>
       <c r="G57" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -6379,11 +6625,13 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Rocket League</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v/>
+          <t>Rocket League®</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Action, Indie, Racing, Sports</t>
+        </is>
       </c>
       <c r="D58" s="2" t="n">
         <v>21106</v>
@@ -6395,7 +6643,7 @@
         <v>583220</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
@@ -6492,31 +6740,33 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Battlefield 2042</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D62" s="2" t="n">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Battlefield™ 2042</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
         <v>2774</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="4" t="n">
         <v>46.7</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="4" t="n">
         <v>297774</v>
       </c>
-      <c r="G62" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>0</v>
+      <c r="G62" s="4" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="63">
@@ -6528,8 +6778,10 @@
           <t>Halo Infinite</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="D63" t="n">
         <v>2275</v>
@@ -6541,7 +6793,7 @@
         <v>177041</v>
       </c>
       <c r="G63" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -6583,11 +6835,13 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SMITE</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v/>
+          <t>SMITE®</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual, Indie, Massively Multiplayer, RPG, Simulation, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="D65" t="n">
         <v>1853</v>
@@ -6599,7 +6853,7 @@
         <v>119796</v>
       </c>
       <c r="G65" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -6614,8 +6868,10 @@
           <t>World of Tanks Blitz</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Strategy, Free To Play</t>
+        </is>
       </c>
       <c r="D66" s="2" t="n">
         <v>5707</v>
@@ -6627,7 +6883,7 @@
         <v>148161</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>0</v>
@@ -6702,8 +6958,10 @@
           <t>Schedule I</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Action, Indie, Simulation, Strategy, Early Access</t>
+        </is>
       </c>
       <c r="D69" t="n">
         <v>22757</v>
@@ -6715,7 +6973,7 @@
         <v>204041</v>
       </c>
       <c r="G69" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -6730,8 +6988,10 @@
           <t>Ring of Elysium</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Action, Free To Play, Massively Multiplayer</t>
+        </is>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
@@ -6743,7 +7003,7 @@
         <v>99837</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>0</v>
@@ -6758,8 +7018,10 @@
           <t>Portal</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D71" t="n">
         <v>638</v>
@@ -6771,7 +7033,7 @@
         <v>177741</v>
       </c>
       <c r="G71" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -6783,11 +7045,13 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>The Sims 4</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v/>
+          <t>The Sims™ 4</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Adventure, Casual, Simulation, Free To Play</t>
+        </is>
       </c>
       <c r="D72" s="2" t="n">
         <v>25276</v>
@@ -6799,7 +7063,7 @@
         <v>170727</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -6814,8 +7078,10 @@
           <t>Black Squad</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Action, Free To Play</t>
+        </is>
       </c>
       <c r="D73" t="n">
         <v>212</v>
@@ -6827,7 +7093,7 @@
         <v>81714</v>
       </c>
       <c r="G73" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -6842,8 +7108,10 @@
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="D74" s="2" t="n">
         <v>30542</v>
@@ -6855,7 +7123,7 @@
         <v>499061</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v/>
+        <v>15500</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
@@ -6870,8 +7138,10 @@
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Action, Adventure, RPG</t>
+        </is>
       </c>
       <c r="D75" t="n">
         <v>4953</v>
@@ -6883,38 +7153,40 @@
         <v>457632</v>
       </c>
       <c r="G75" t="n">
-        <v/>
+        <v>27400</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D76" s="2" t="n">
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Adventure, Casual, Indie, Simulation</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="4" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="4" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>0</v>
+      <c r="G76" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="77">
@@ -6926,8 +7198,10 @@
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="D77" t="n">
         <v>17045</v>
@@ -6939,7 +7213,7 @@
         <v>370046</v>
       </c>
       <c r="G77" t="n">
-        <v/>
+        <v>47000</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -6981,11 +7255,13 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eFootball</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v/>
+          <t>eFootball™</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Simulation, Sports, Free To Play</t>
+        </is>
       </c>
       <c r="D79" t="n">
         <v>13404</v>
@@ -6997,7 +7273,7 @@
         <v>92333</v>
       </c>
       <c r="G79" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -7012,8 +7288,10 @@
           <t>Street Warriors Online</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Action, Massively Multiplayer, Simulation, Sports</t>
+        </is>
       </c>
       <c r="D80" s="2" t="n">
         <v>1</v>
@@ -7025,7 +7303,7 @@
         <v>1634</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v/>
+        <v>2200</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
@@ -7040,8 +7318,10 @@
           <t>Z1 Battle Royale</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Free To Play, Massively Multiplayer</t>
+        </is>
       </c>
       <c r="D81" t="n">
         <v>1010</v>
@@ -7053,7 +7333,7 @@
         <v>204013</v>
       </c>
       <c r="G81" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -7068,8 +7348,10 @@
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D82" s="2" t="n">
         <v>6300</v>
@@ -7081,7 +7363,7 @@
         <v>248220</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v/>
+        <v>36700</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>0</v>
@@ -7093,11 +7375,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sekiro: Shadows Die Twice - GOTY Edition</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v/>
+          <t>Sekiro™: Shadows Die Twice - GOTY Edition</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Action, Adventure</t>
+        </is>
       </c>
       <c r="D83" t="n">
         <v>6767</v>
@@ -7109,7 +7393,7 @@
         <v>322234</v>
       </c>
       <c r="G83" t="n">
-        <v/>
+        <v>75000</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -7124,8 +7408,10 @@
           <t>CyberCorp</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="D84" s="2" t="n">
         <v>3</v>
@@ -7137,7 +7423,7 @@
         <v>322</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v/>
+        <v>16500</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
@@ -7152,8 +7438,10 @@
           <t>Half-Life 2</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
       </c>
       <c r="D85" t="n">
         <v>1555</v>
@@ -7165,7 +7453,7 @@
         <v>245627</v>
       </c>
       <c r="G85" t="n">
-        <v/>
+        <v>11000</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -7180,8 +7468,10 @@
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Action, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="D86" s="2" t="n">
         <v>7181</v>
@@ -7193,7 +7483,7 @@
         <v>283264</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v/>
+        <v>36000</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>0</v>
@@ -7238,8 +7528,10 @@
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG</t>
+        </is>
       </c>
       <c r="D88" s="2" t="n">
         <v>2376</v>
@@ -7251,7 +7543,7 @@
         <v>99730</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v/>
+        <v>26500</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>0</v>
@@ -7266,8 +7558,10 @@
           <t>Cities: Skylines</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Simulation, Strategy</t>
+        </is>
       </c>
       <c r="D89" t="n">
         <v>8842</v>
@@ -7279,7 +7573,7 @@
         <v>275770</v>
       </c>
       <c r="G89" t="n">
-        <v/>
+        <v>33000</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -7294,8 +7588,10 @@
           <t>Mount &amp; Blade II: Bannerlord</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Action, Indie, RPG, Simulation, Strategy</t>
+        </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>14477</v>
@@ -7307,7 +7603,7 @@
         <v>264391</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v/>
+        <v>60000</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
@@ -7319,11 +7615,13 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sid Meier's Civilization V</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v/>
+          <t>Sid Meier's Civilization® V</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
       </c>
       <c r="D91" t="n">
         <v>12206</v>
@@ -7335,7 +7633,7 @@
         <v>204265</v>
       </c>
       <c r="G91" t="n">
-        <v/>
+        <v>32000</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -7350,8 +7648,10 @@
           <t>Trove</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Casual, Massively Multiplayer, RPG, Free To Play</t>
+        </is>
       </c>
       <c r="D92" s="2" t="n">
         <v>758</v>
@@ -7363,7 +7663,7 @@
         <v>92370</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>0</v>
@@ -7375,11 +7675,13 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sid Meier’s Civilization VI</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v/>
+          <t>Sid Meier’s Civilization® VI</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
       </c>
       <c r="D93" t="n">
         <v>25420</v>
@@ -7391,7 +7693,7 @@
         <v>349920</v>
       </c>
       <c r="G93" t="n">
-        <v/>
+        <v>65000</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -7406,8 +7708,10 @@
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>RPG</t>
+        </is>
       </c>
       <c r="D94" s="2" t="n">
         <v>11179</v>
@@ -7419,7 +7723,7 @@
         <v>392287</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v/>
+        <v>22000</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>0</v>
@@ -7434,8 +7738,10 @@
           <t>Life is Strange 2</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
       </c>
       <c r="D95" t="n">
         <v>153</v>
@@ -7447,66 +7753,70 @@
         <v>36634</v>
       </c>
       <c r="G95" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Warhammer 40,000: Rogue Trader</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Indie, RPG, Strategy</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="n">
         <v>3582</v>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" s="4" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="F96" s="2" t="n">
+      <c r="F96" s="4" t="n">
         <v>30805</v>
       </c>
-      <c r="G96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>0</v>
+      <c r="G96" s="4" t="n">
+        <v>15900</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Battlefield V</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v/>
-      </c>
-      <c r="D97" t="n">
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Battlefield™ V</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="n">
         <v>6327</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="4" t="n">
         <v>250288</v>
       </c>
-      <c r="G97" t="n">
-        <v/>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
+      <c r="G97" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="98">
@@ -7548,8 +7858,10 @@
           <t>DayZ</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Massively Multiplayer</t>
+        </is>
       </c>
       <c r="D99" t="n">
         <v>37066</v>
@@ -7561,38 +7873,40 @@
         <v>430252</v>
       </c>
       <c r="G99" t="n">
-        <v/>
+        <v>59000</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Adventure, Indie, Simulation, Strategy</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="n">
         <v>12596</v>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" s="4" t="n">
         <v>97.2</v>
       </c>
-      <c r="F100" s="2" t="n">
+      <c r="F100" s="4" t="n">
         <v>232064</v>
       </c>
-      <c r="G100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
+      <c r="G100" s="4" t="n">
+        <v>29400</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="101">
@@ -7634,8 +7948,10 @@
           <t>Risk of Rain 2</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Action, Indie</t>
+        </is>
       </c>
       <c r="D102" s="2" t="n">
         <v>7902</v>
@@ -7647,7 +7963,7 @@
         <v>313577</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v/>
+        <v>26000</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>0</v>
@@ -7659,11 +7975,13 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EA SPORTS FIFA 23</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v/>
+          <t>EA SPORTS™ FIFA 23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Simulation, Sports</t>
+        </is>
       </c>
       <c r="D103" t="n">
         <v>1280</v>
@@ -7675,7 +7993,7 @@
         <v>151419</v>
       </c>
       <c r="G103" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -7711,9 +8029,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-27</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7785,7 +8103,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>아직 7일 분량의 데이터가 쌓이지 않았습니다. 매일 자동 수집이 진행되면 이 시트가 채워집니다.</t>
         </is>
@@ -7821,9 +8139,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-27</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7895,7 +8213,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>아직 14일 분량의 데이터가 쌓이지 않았습니다. 매일 자동 수집이 진행되면 이 시트가 채워집니다.</t>
         </is>
@@ -7931,9 +8249,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-27</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8323,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>아직 28일 분량의 데이터가 쌓이지 않았습니다. 매일 자동 수집이 진행되면 이 시트가 채워집니다.</t>
         </is>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3119,10 +3119,10 @@
         <v>139186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6600</v>
+        <v>66000</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>66000</v>
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3735,10 +3735,10 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6150</v>
+        <v>20500</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>20500</v>
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4659,10 +4659,10 @@
         <v>177352</v>
       </c>
       <c r="J95" t="n">
-        <v>5500</v>
+        <v>55000</v>
       </c>
       <c r="K95" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>55000</v>
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-28</t>
+          <t>Steam 인기 차트 — 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -6740,33 +6740,33 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Battlefield™ 2042</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Casual</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="2" t="n">
         <v>2774</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="2" t="n">
         <v>46.7</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="2" t="n">
         <v>297774</v>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>90</v>
+      <c r="G62" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7160,33 +7160,33 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="2" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="2" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>6150</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>70</v>
+      <c r="G76" s="2" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -7790,33 +7790,33 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" t="n">
         <v>94</v>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Battlefield™ V</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="D97" t="n">
         <v>6327</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" t="n">
         <v>250288</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>90</v>
+      <c r="G97" t="n">
+        <v>55000</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-28</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-28</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-28</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-29</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The Witcher 3: Wild Hunt - Complete Edition</t>
+          <t>The Witcher 3: Wild Hunt — Remastered</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-29</t>
+          <t>Steam 인기 차트 — 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>The Witcher 3: Wild Hunt - Complete Edition</t>
+          <t>The Witcher 3: Wild Hunt — Remastered</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-29</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-29</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-29</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-30</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-30</t>
+          <t>Steam 인기 차트 — 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-09-30</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-09-30</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-09-30</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-01</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -705,10 +705,10 @@
         <v>358266</v>
       </c>
       <c r="J5" t="n">
-        <v>32000</v>
+        <v>22400</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
         <v>32000</v>
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -969,10 +969,10 @@
         <v>940221</v>
       </c>
       <c r="J11" t="n">
-        <v>11000</v>
+        <v>2200</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L11" t="n">
         <v>11000</v>
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1143,10 +1143,10 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v>45800</v>
+        <v>34350</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
         <v>45800</v>
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1187,10 +1187,10 @@
         <v>775883</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>44800</v>
+        <v>33600</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>44800</v>
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1319,10 +1319,10 @@
         <v>1373979</v>
       </c>
       <c r="J19" t="n">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
         <v>11000</v>
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1405,10 +1405,10 @@
         <v>876898</v>
       </c>
       <c r="J21" t="n">
-        <v>5600</v>
+        <v>4480</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L21" t="n">
         <v>5600</v>
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1449,10 +1449,10 @@
         <v>736688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>66000</v>
+        <v>46200</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>66000</v>
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1537,10 +1537,10 @@
         <v>1122546</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10500</v>
+        <v>5250</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>10500</v>
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1669,10 +1669,10 @@
         <v>1071135</v>
       </c>
       <c r="J27" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" t="n">
         <v>42000</v>
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1757,10 +1757,10 @@
         <v>612177</v>
       </c>
       <c r="J29" t="n">
-        <v>16500</v>
+        <v>10890</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L29" t="n">
         <v>16500</v>
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1801,10 +1801,10 @@
         <v>872384</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16000</v>
+        <v>11200</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>16000</v>
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1845,10 +1845,10 @@
         <v>599805</v>
       </c>
       <c r="J31" t="n">
-        <v>20500</v>
+        <v>4300</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="L31" t="n">
         <v>20500</v>
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1975,10 +1975,10 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10700</v>
+        <v>5350</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>10700</v>
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2107,10 +2107,10 @@
         <v>88027</v>
       </c>
       <c r="J37" t="n">
-        <v>37500</v>
+        <v>26250</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
         <v>37500</v>
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2195,10 +2195,10 @@
         <v>713071</v>
       </c>
       <c r="J39" t="n">
-        <v>66000</v>
+        <v>19800</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L39" t="n">
         <v>66000</v>
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2239,10 +2239,10 @@
         <v>630223</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21500</v>
+        <v>8600</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>21500</v>
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2283,10 +2283,10 @@
         <v>289966</v>
       </c>
       <c r="J41" t="n">
-        <v>79800</v>
+        <v>7980</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L41" t="n">
         <v>79800</v>
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2415,10 +2415,10 @@
         <v>643681</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>5500</v>
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2503,19 +2503,19 @@
         <v>272900</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6450</v>
+        <v>5250</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>43000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2591,10 +2591,10 @@
         <v>471451</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32000</v>
+        <v>28800</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>32000</v>
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2635,10 +2635,10 @@
         <v>736611</v>
       </c>
       <c r="J49" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L49" t="n">
         <v>21500</v>
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2811,10 +2811,10 @@
         <v>143086</v>
       </c>
       <c r="J53" t="n">
-        <v>10500</v>
+        <v>2100</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L53" t="n">
         <v>10500</v>
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2855,10 +2855,10 @@
         <v>434239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>36800</v>
+        <v>9570</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>36800</v>
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2987,10 +2987,10 @@
         <v>355171</v>
       </c>
       <c r="J57" t="n">
-        <v>26500</v>
+        <v>17750</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L57" t="n">
         <v>26500</v>
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3075,10 +3075,10 @@
         <v>676667</v>
       </c>
       <c r="J59" t="n">
-        <v>73000</v>
+        <v>18250</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L59" t="n">
         <v>73000</v>
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3119,10 +3119,10 @@
         <v>139186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>66000</v>
+        <v>6600</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>66000</v>
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3207,10 +3207,10 @@
         <v>323198</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21000</v>
+        <v>14070</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>21000</v>
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3339,10 +3339,10 @@
         <v>243818</v>
       </c>
       <c r="J65" t="n">
-        <v>10500</v>
+        <v>2100</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L65" t="n">
         <v>10500</v>
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3383,10 +3383,10 @@
         <v>175426</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>11000</v>
+        <v>2200</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>11000</v>
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3427,10 +3427,10 @@
         <v>200803</v>
       </c>
       <c r="J67" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L67" t="n">
         <v>21500</v>
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3515,10 +3515,10 @@
         <v>175024</v>
       </c>
       <c r="J69" t="n">
-        <v>11000</v>
+        <v>2200</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L69" t="n">
         <v>11000</v>
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3647,10 +3647,10 @@
         <v>475393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15500</v>
+        <v>5270</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>15500</v>
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3691,10 +3691,10 @@
         <v>435687</v>
       </c>
       <c r="J73" t="n">
-        <v>27400</v>
+        <v>2740</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L73" t="n">
         <v>27400</v>
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3735,10 +3735,10 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>20500</v>
+        <v>6150</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>20500</v>
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3779,10 +3779,10 @@
         <v>327889</v>
       </c>
       <c r="J75" t="n">
-        <v>47000</v>
+        <v>25850</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L75" t="n">
         <v>47000</v>
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3823,10 +3823,10 @@
         <v>13442</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>10500</v>
+        <v>2100</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>10500</v>
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3999,10 +3999,10 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36700</v>
+        <v>14680</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>36700</v>
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4043,10 +4043,10 @@
         <v>307041</v>
       </c>
       <c r="J81" t="n">
-        <v>75000</v>
+        <v>37500</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L81" t="n">
         <v>75000</v>
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4087,10 +4087,10 @@
         <v>266</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>16500</v>
+        <v>8250</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>16500</v>
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4131,10 +4131,10 @@
         <v>239721</v>
       </c>
       <c r="J83" t="n">
-        <v>11000</v>
+        <v>2200</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L83" t="n">
         <v>11000</v>
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4175,10 +4175,10 @@
         <v>256128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>36000</v>
+        <v>9000</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>36000</v>
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4219,10 +4219,10 @@
         <v>222495</v>
       </c>
       <c r="J85" t="n">
-        <v>32000</v>
+        <v>9280</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L85" t="n">
         <v>32000</v>
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4263,10 +4263,10 @@
         <v>93489</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>26500</v>
+        <v>3970</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>26500</v>
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4307,10 +4307,10 @@
         <v>256362</v>
       </c>
       <c r="J87" t="n">
-        <v>33000</v>
+        <v>9900</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L87" t="n">
         <v>33000</v>
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4351,10 +4351,10 @@
         <v>232360</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>60000</v>
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4395,10 +4395,10 @@
         <v>195724</v>
       </c>
       <c r="J89" t="n">
-        <v>32000</v>
+        <v>8000</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L89" t="n">
         <v>32000</v>
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4483,10 +4483,10 @@
         <v>304053</v>
       </c>
       <c r="J91" t="n">
-        <v>65000</v>
+        <v>6500</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L91" t="n">
         <v>65000</v>
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4527,10 +4527,10 @@
         <v>326054</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>22000</v>
+        <v>8800</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>22000</v>
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4659,10 +4659,10 @@
         <v>177352</v>
       </c>
       <c r="J95" t="n">
-        <v>55000</v>
+        <v>5500</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L95" t="n">
         <v>55000</v>
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4703,10 +4703,10 @@
         <v>179154</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>10700</v>
+        <v>6950</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>10700</v>
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4747,10 +4747,10 @@
         <v>330349</v>
       </c>
       <c r="J97" t="n">
-        <v>59000</v>
+        <v>29500</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L97" t="n">
         <v>59000</v>
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4879,10 +4879,10 @@
         <v>293127</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>26000</v>
+        <v>8580</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>26000</v>
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-01</t>
+          <t>Steam 인기 차트 — 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5096,33 +5096,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>18028</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="4" t="n">
         <v>380709</v>
       </c>
-      <c r="G7" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
+      <c r="G7" s="4" t="n">
+        <v>22400</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -5276,33 +5276,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>25122</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="4" t="n">
         <v>963983</v>
       </c>
-      <c r="G13" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
+      <c r="G13" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -5394,63 +5394,63 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="G17" t="n">
-        <v>45800</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+      <c r="G17" s="4" t="n">
+        <v>34350</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>HELLDIVERS™ 2</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="4" t="n">
         <v>53399</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="4" t="n">
         <v>76.2</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="4" t="n">
         <v>1017635</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>44800</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
+      <c r="G18" s="4" t="n">
+        <v>33600</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -5514,33 +5514,33 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>24580</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="4" t="n">
         <v>1409473</v>
       </c>
-      <c r="G21" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
+      <c r="G21" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -5572,63 +5572,63 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Casual, Indie, Animation &amp; Modeling, Design &amp; Illustration, Photo Editing, Utilities</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>91184</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="4" t="n">
         <v>894458</v>
       </c>
-      <c r="G23" t="n">
-        <v>5600</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
+      <c r="G23" s="4" t="n">
+        <v>4480</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Adventure, RPG, Strategy</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="4" t="n">
         <v>54771</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="4" t="n">
         <v>760662</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
+      <c r="G24" s="4" t="n">
+        <v>46200</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -5662,33 +5662,33 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="4" t="n">
         <v>18400</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="4" t="n">
         <v>1159707</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
+      <c r="G26" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -5752,33 +5752,33 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>143870</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>87.2</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="4" t="n">
         <v>1227784</v>
       </c>
-      <c r="G29" t="n">
-        <v>42000</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
+      <c r="G29" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -5812,93 +5812,93 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>22170</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>83.8</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="4" t="n">
         <v>730170</v>
       </c>
-      <c r="G31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
+      <c r="G31" s="4" t="n">
+        <v>10890</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Indie, RPG, Simulation</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="4" t="n">
         <v>50662</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="4" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="4" t="n">
         <v>886195</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>16000</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
+      <c r="G32" s="4" t="n">
+        <v>11200</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>2892</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>95.5</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="4" t="n">
         <v>627791</v>
       </c>
-      <c r="G33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
+      <c r="G33" s="4" t="n">
+        <v>4300</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -5960,33 +5960,33 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="4" t="n">
         <v>27254</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="4" t="n">
         <v>663082</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
+      <c r="G36" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -6050,33 +6050,33 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>5831</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="4" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="4" t="n">
         <v>110623</v>
       </c>
-      <c r="G39" t="n">
-        <v>37500</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
+      <c r="G39" s="4" t="n">
+        <v>26250</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -6110,93 +6110,93 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>22265</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="4" t="n">
         <v>844921</v>
       </c>
-      <c r="G41" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
+      <c r="G41" s="4" t="n">
+        <v>19800</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="4" t="n">
         <v>44886</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="4" t="n">
         <v>797216</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>21500</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
+      <c r="G42" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>5716</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>90.2</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="4" t="n">
         <v>321395</v>
       </c>
-      <c r="G43" t="n">
-        <v>79800</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
+      <c r="G43" s="4" t="n">
+        <v>7980</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="44">
@@ -6260,33 +6260,33 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Casual</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="4" t="n">
         <v>3832</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="4" t="n">
         <v>700785</v>
       </c>
-      <c r="G46" s="2" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
+      <c r="G46" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -6343,10 +6343,10 @@
         <v>295218</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>6450</v>
+        <v>5250</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -6380,63 +6380,63 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="4" t="n">
         <v>14439</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="4" t="n">
         <v>94.3</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="4" t="n">
         <v>499828</v>
       </c>
-      <c r="G50" s="2" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
+      <c r="G50" s="4" t="n">
+        <v>28800</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Action, Indie, Early Access</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>9978</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="4" t="n">
         <v>768779</v>
       </c>
-      <c r="G51" t="n">
-        <v>21500</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
+      <c r="G51" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -6530,63 +6530,63 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Half-Life</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>634</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="4" t="n">
         <v>96.5</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="4" t="n">
         <v>148221</v>
       </c>
-      <c r="G55" t="n">
-        <v>10500</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
+      <c r="G55" s="4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="4" t="n">
         <v>11923</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="4" t="n">
         <v>493390</v>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
+      <c r="G56" s="4" t="n">
+        <v>9570</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -6650,33 +6650,33 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Project Zomboid</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Indie, RPG, Simulation, Early Access</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>22864</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="4" t="n">
         <v>94.2</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="4" t="n">
         <v>377063</v>
       </c>
-      <c r="G59" t="n">
-        <v>26500</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
+      <c r="G59" s="4" t="n">
+        <v>17750</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="60">
@@ -6710,63 +6710,63 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Red Dead Redemption 2</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>29885</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="4" t="n">
         <v>92.2</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="4" t="n">
         <v>733542</v>
       </c>
-      <c r="G61" t="n">
-        <v>73000</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
+      <c r="G61" s="4" t="n">
+        <v>18250</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Battlefield™ 2042</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Casual</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="4" t="n">
         <v>2774</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="4" t="n">
         <v>46.7</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="4" t="n">
         <v>297774</v>
       </c>
-      <c r="G62" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>0</v>
+      <c r="G62" s="4" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="63">
@@ -6800,33 +6800,33 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Raft</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="4" t="n">
         <v>4701</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="4" t="n">
         <v>93.3</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="4" t="n">
         <v>346359</v>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>0</v>
+      <c r="G64" s="4" t="n">
+        <v>14070</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="65">
@@ -6890,93 +6890,93 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Counter-Strike</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="4" t="n">
         <v>7323</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="4" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="4" t="n">
         <v>250245</v>
       </c>
-      <c r="G67" t="n">
-        <v>10500</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
+      <c r="G67" s="4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Counter-Strike: Source</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="4" t="n">
         <v>6187</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="4" t="n">
         <v>96.3</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="4" t="n">
         <v>182234</v>
       </c>
-      <c r="G68" s="2" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>0</v>
+      <c r="G68" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Schedule I</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Action, Indie, Simulation, Strategy, Early Access</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="4" t="n">
         <v>22757</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="4" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="4" t="n">
         <v>204041</v>
       </c>
-      <c r="G69" t="n">
-        <v>21500</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
+      <c r="G69" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -7010,33 +7010,33 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>638</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="4" t="n">
         <v>98.5</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="4" t="n">
         <v>177741</v>
       </c>
-      <c r="G71" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
+      <c r="G71" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="72">
@@ -7100,153 +7100,153 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="4" t="n">
         <v>30542</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="4" t="n">
         <v>95.3</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="4" t="n">
         <v>499061</v>
       </c>
-      <c r="G74" s="2" t="n">
-        <v>15500</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>0</v>
+      <c r="G74" s="4" t="n">
+        <v>5270</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>4953</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="4" t="n">
         <v>95.2</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="4" t="n">
         <v>457632</v>
       </c>
-      <c r="G75" t="n">
-        <v>27400</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
+      <c r="G75" s="4" t="n">
+        <v>2740</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="4" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="4" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="4" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="2" t="n">
-        <v>20500</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>0</v>
+      <c r="G76" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>17045</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="4" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="4" t="n">
         <v>370046</v>
       </c>
-      <c r="G77" t="n">
-        <v>47000</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
+      <c r="G77" s="4" t="n">
+        <v>25850</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Counter-Strike: Condition Zero</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="4" t="n">
         <v>89.8</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="4" t="n">
         <v>14977</v>
       </c>
-      <c r="G78" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
+      <c r="G78" s="4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="79">
@@ -7340,303 +7340,303 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="4" t="n">
         <v>6300</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="4" t="n">
         <v>248220</v>
       </c>
-      <c r="G82" s="2" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>0</v>
+      <c r="G82" s="4" t="n">
+        <v>14680</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Sekiro™: Shadows Die Twice - GOTY Edition</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>6767</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="4" t="n">
         <v>95.3</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="4" t="n">
         <v>322234</v>
       </c>
-      <c r="G83" t="n">
-        <v>75000</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
+      <c r="G83" s="4" t="n">
+        <v>37500</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>CyberCorp</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E84" s="4" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="4" t="n">
         <v>322</v>
       </c>
-      <c r="G84" s="2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>0</v>
+      <c r="G84" s="4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Half-Life 2</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>1555</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="4" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="4" t="n">
         <v>245627</v>
       </c>
-      <c r="G85" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
+      <c r="G85" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Action, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="4" t="n">
         <v>7181</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" s="4" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="4" t="n">
         <v>283264</v>
       </c>
-      <c r="G86" s="2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>0</v>
+      <c r="G86" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Sons Of The Forest</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>4450</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="4" t="n">
         <v>87.8</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="4" t="n">
         <v>253546</v>
       </c>
-      <c r="G87" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
+      <c r="G87" s="4" t="n">
+        <v>9280</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="4" t="n">
         <v>2376</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" s="4" t="n">
         <v>93.7</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="4" t="n">
         <v>99730</v>
       </c>
-      <c r="G88" s="2" t="n">
-        <v>26500</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>0</v>
+      <c r="G88" s="4" t="n">
+        <v>3970</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Cities: Skylines</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>8842</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" s="4" t="n">
         <v>275770</v>
       </c>
-      <c r="G89" t="n">
-        <v>33000</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
+      <c r="G89" s="4" t="n">
+        <v>9900</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Mount &amp; Blade II: Bannerlord</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>Action, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="4" t="n">
         <v>14477</v>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="4" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F90" s="4" t="n">
         <v>264391</v>
       </c>
-      <c r="G90" s="2" t="n">
-        <v>60000</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>0</v>
+      <c r="G90" s="4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Sid Meier's Civilization® V</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="4" t="n">
         <v>12206</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="4" t="n">
         <v>204265</v>
       </c>
-      <c r="G91" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
+      <c r="G91" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="92">
@@ -7670,63 +7670,63 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Sid Meier’s Civilization® VI</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>25420</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="4" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="4" t="n">
         <v>349920</v>
       </c>
-      <c r="G93" t="n">
-        <v>65000</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
+      <c r="G93" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="4" t="n">
         <v>11179</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" s="4" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="4" t="n">
         <v>392287</v>
       </c>
-      <c r="G94" s="2" t="n">
-        <v>22000</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>0</v>
+      <c r="G94" s="4" t="n">
+        <v>8800</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="95">
@@ -7790,93 +7790,93 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Battlefield™ V</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>6327</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="4" t="n">
         <v>250288</v>
       </c>
-      <c r="G97" t="n">
-        <v>55000</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
+      <c r="G97" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>R.E.P.O.</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Action, Early Access</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="4" t="n">
         <v>32349</v>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E98" s="4" t="n">
         <v>96.5</v>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="4" t="n">
         <v>185642</v>
       </c>
-      <c r="G98" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
+      <c r="G98" s="4" t="n">
+        <v>6950</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>DayZ</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Massively Multiplayer</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>37066</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="4" t="n">
         <v>76.8</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="4" t="n">
         <v>430252</v>
       </c>
-      <c r="G99" t="n">
-        <v>59000</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
+      <c r="G99" s="4" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="100">
@@ -7940,33 +7940,33 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Risk of Rain 2</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>Action, Indie</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="4" t="n">
         <v>7902</v>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="4" t="n">
         <v>93.5</v>
       </c>
-      <c r="F102" s="2" t="n">
+      <c r="F102" s="4" t="n">
         <v>313577</v>
       </c>
-      <c r="G102" s="2" t="n">
-        <v>26000</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>0</v>
+      <c r="G102" s="4" t="n">
+        <v>8580</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="103">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-01</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-01</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-01</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-02</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-02</t>
+          <t>Steam 인기 차트 — 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-02</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-02</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-02</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-03</t>
+          <t>Steam 인기 차트 — 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-03</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-03</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-03</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-04</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-04</t>
+          <t>Steam 인기 차트 — 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-04</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-04</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-04</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-05</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-05</t>
+          <t>Steam 인기 차트 — 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-05</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-05</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-05</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-06</t>
+          <t>Steam 인기 차트 — 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-06</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-06</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-06</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-07</t>
+          <t>Steam 인기 차트 — 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-07</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-07</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-07</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -969,10 +969,10 @@
         <v>940221</v>
       </c>
       <c r="J11" t="n">
-        <v>2200</v>
+        <v>11000</v>
       </c>
       <c r="K11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>11000</v>
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1143,10 +1143,10 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v>34350</v>
+        <v>45800</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>45800</v>
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1187,10 +1187,10 @@
         <v>775883</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33600</v>
+        <v>44800</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>44800</v>
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1405,10 +1405,10 @@
         <v>876898</v>
       </c>
       <c r="J21" t="n">
-        <v>4480</v>
+        <v>5600</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>5600</v>
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1449,10 +1449,10 @@
         <v>736688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46200</v>
+        <v>66000</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>66000</v>
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1537,10 +1537,10 @@
         <v>1122546</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5250</v>
+        <v>10500</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>10500</v>
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1669,10 +1669,10 @@
         <v>1071135</v>
       </c>
       <c r="J27" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>42000</v>
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1757,10 +1757,10 @@
         <v>612177</v>
       </c>
       <c r="J29" t="n">
-        <v>10890</v>
+        <v>16500</v>
       </c>
       <c r="K29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>16500</v>
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1801,10 +1801,10 @@
         <v>872384</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11200</v>
+        <v>16000</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>16000</v>
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1845,10 +1845,10 @@
         <v>599805</v>
       </c>
       <c r="J31" t="n">
-        <v>4300</v>
+        <v>20500</v>
       </c>
       <c r="K31" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>20500</v>
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1975,10 +1975,10 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5350</v>
+        <v>10700</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>10700</v>
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2107,10 +2107,10 @@
         <v>88027</v>
       </c>
       <c r="J37" t="n">
-        <v>26250</v>
+        <v>37500</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>37500</v>
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2195,10 +2195,10 @@
         <v>713071</v>
       </c>
       <c r="J39" t="n">
-        <v>19800</v>
+        <v>66000</v>
       </c>
       <c r="K39" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>66000</v>
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2239,10 +2239,10 @@
         <v>630223</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8600</v>
+        <v>21500</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>21500</v>
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2283,10 +2283,10 @@
         <v>289966</v>
       </c>
       <c r="J41" t="n">
-        <v>7980</v>
+        <v>79800</v>
       </c>
       <c r="K41" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>79800</v>
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2371,10 +2371,10 @@
         <v>802993</v>
       </c>
       <c r="J43" t="n">
-        <v>27450</v>
+        <v>54900</v>
       </c>
       <c r="K43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>54900</v>
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2503,10 +2503,10 @@
         <v>272900</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5250</v>
+        <v>21000</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>21000</v>
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2547,19 +2547,19 @@
         <v>844480</v>
       </c>
       <c r="J47" t="n">
-        <v>6200</v>
+        <v>27000</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>24800</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2591,10 +2591,10 @@
         <v>471451</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28800</v>
+        <v>32000</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>32000</v>
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2635,10 +2635,10 @@
         <v>736611</v>
       </c>
       <c r="J49" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="K49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>21500</v>
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2811,19 +2811,19 @@
         <v>143086</v>
       </c>
       <c r="J53" t="n">
-        <v>2100</v>
+        <v>11000</v>
       </c>
       <c r="K53" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2855,10 +2855,10 @@
         <v>434239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9570</v>
+        <v>36800</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>36800</v>
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2987,10 +2987,10 @@
         <v>355171</v>
       </c>
       <c r="J57" t="n">
-        <v>17750</v>
+        <v>26500</v>
       </c>
       <c r="K57" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>26500</v>
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3119,10 +3119,10 @@
         <v>139186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6600</v>
+        <v>66000</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>66000</v>
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3207,10 +3207,10 @@
         <v>323198</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14070</v>
+        <v>21000</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>21000</v>
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3339,19 +3339,19 @@
         <v>243818</v>
       </c>
       <c r="J65" t="n">
-        <v>2100</v>
+        <v>11000</v>
       </c>
       <c r="K65" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3383,10 +3383,10 @@
         <v>175426</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2200</v>
+        <v>11000</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>11000</v>
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3427,10 +3427,10 @@
         <v>200803</v>
       </c>
       <c r="J67" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="K67" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>21500</v>
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3515,10 +3515,10 @@
         <v>175024</v>
       </c>
       <c r="J69" t="n">
-        <v>2200</v>
+        <v>11000</v>
       </c>
       <c r="K69" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>11000</v>
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3647,10 +3647,10 @@
         <v>475393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5270</v>
+        <v>15500</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>15500</v>
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3691,10 +3691,10 @@
         <v>435687</v>
       </c>
       <c r="J73" t="n">
-        <v>2740</v>
+        <v>27400</v>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>27400</v>
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3735,10 +3735,10 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6150</v>
+        <v>20500</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>20500</v>
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3779,10 +3779,10 @@
         <v>327889</v>
       </c>
       <c r="J75" t="n">
-        <v>25850</v>
+        <v>47000</v>
       </c>
       <c r="K75" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>47000</v>
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3823,19 +3823,19 @@
         <v>13442</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2100</v>
+        <v>11000</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3999,10 +3999,10 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>14680</v>
+        <v>36700</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>36700</v>
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4087,10 +4087,10 @@
         <v>266</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>8250</v>
+        <v>16500</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>16500</v>
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4131,10 +4131,10 @@
         <v>239721</v>
       </c>
       <c r="J83" t="n">
-        <v>2200</v>
+        <v>11000</v>
       </c>
       <c r="K83" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>11000</v>
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4175,10 +4175,10 @@
         <v>256128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>9000</v>
+        <v>36000</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>36000</v>
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4219,10 +4219,10 @@
         <v>222495</v>
       </c>
       <c r="J85" t="n">
-        <v>9280</v>
+        <v>32000</v>
       </c>
       <c r="K85" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>32000</v>
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4263,10 +4263,10 @@
         <v>93489</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3970</v>
+        <v>26500</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>26500</v>
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4307,10 +4307,10 @@
         <v>256362</v>
       </c>
       <c r="J87" t="n">
-        <v>9900</v>
+        <v>33000</v>
       </c>
       <c r="K87" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>33000</v>
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4351,10 +4351,10 @@
         <v>232360</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>60000</v>
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4395,10 +4395,10 @@
         <v>195724</v>
       </c>
       <c r="J89" t="n">
-        <v>8000</v>
+        <v>32000</v>
       </c>
       <c r="K89" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>32000</v>
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4483,10 +4483,10 @@
         <v>304053</v>
       </c>
       <c r="J91" t="n">
-        <v>6500</v>
+        <v>65000</v>
       </c>
       <c r="K91" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>65000</v>
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4527,10 +4527,10 @@
         <v>326054</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>8800</v>
+        <v>22000</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>22000</v>
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4615,10 +4615,10 @@
         <v>26360</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>15900</v>
+        <v>53000</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>53000</v>
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4659,10 +4659,10 @@
         <v>177352</v>
       </c>
       <c r="J95" t="n">
-        <v>5500</v>
+        <v>55000</v>
       </c>
       <c r="K95" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>55000</v>
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4703,10 +4703,10 @@
         <v>179154</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6950</v>
+        <v>10700</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>10700</v>
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4747,10 +4747,10 @@
         <v>330349</v>
       </c>
       <c r="J97" t="n">
-        <v>29500</v>
+        <v>59000</v>
       </c>
       <c r="K97" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>59000</v>
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4791,10 +4791,10 @@
         <v>225479</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>29400</v>
+        <v>42000</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>42000</v>
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-08</t>
+          <t>Steam 인기 차트 — 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5276,33 +5276,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" t="n">
         <v>25122</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" t="n">
         <v>97.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" t="n">
         <v>963983</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>80</v>
+      <c r="G13" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5394,63 +5394,63 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>12494</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>58.3</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" t="n">
         <v>218415</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>34350</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>25</v>
+      <c r="G17" t="n">
+        <v>45800</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>HELLDIVERS™ 2</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="2" t="n">
         <v>53399</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>76.2</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="2" t="n">
         <v>1017635</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>33600</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>25</v>
+      <c r="G18" s="2" t="n">
+        <v>44800</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5572,63 +5572,63 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Casual, Indie, Animation &amp; Modeling, Design &amp; Illustration, Photo Editing, Utilities</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" t="n">
         <v>91184</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" t="n">
         <v>98</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" t="n">
         <v>894458</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>4480</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>20</v>
+      <c r="G23" t="n">
+        <v>5600</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Adventure, RPG, Strategy</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="2" t="n">
         <v>54771</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="2" t="n">
         <v>760662</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>46200</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>30</v>
+      <c r="G24" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -5662,33 +5662,33 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>18400</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="2" t="n">
         <v>1159707</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>50</v>
+      <c r="G26" s="2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5752,33 +5752,33 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" t="n">
         <v>143870</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>87.2</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" t="n">
         <v>1227784</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>50</v>
+      <c r="G29" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5812,93 +5812,93 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>22170</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>83.8</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" t="n">
         <v>730170</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>10890</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>34</v>
+      <c r="G31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Indie, RPG, Simulation</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="2" t="n">
         <v>50662</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="2" t="n">
         <v>886195</v>
       </c>
-      <c r="G32" s="4" t="n">
-        <v>11200</v>
-      </c>
-      <c r="H32" s="4" t="n">
+      <c r="G32" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>2892</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>95.5</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" t="n">
         <v>627791</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>4300</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>79</v>
+      <c r="G33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -5960,33 +5960,33 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="2" t="n">
         <v>27254</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="2" t="n">
         <v>663082</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>5350</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>50</v>
+      <c r="G36" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -6050,33 +6050,33 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" t="n">
         <v>5831</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" t="n">
         <v>110623</v>
       </c>
-      <c r="G39" s="4" t="n">
-        <v>26250</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>30</v>
+      <c r="G39" t="n">
+        <v>37500</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6110,93 +6110,93 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" t="n">
         <v>22265</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" t="n">
         <v>844921</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>19800</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>70</v>
+      <c r="G41" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="2" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="2" t="n">
         <v>797216</v>
       </c>
-      <c r="G42" s="4" t="n">
-        <v>8600</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>60</v>
+      <c r="G42" s="2" t="n">
+        <v>21500</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" t="n">
         <v>5716</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" t="n">
         <v>90.2</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" t="n">
         <v>321395</v>
       </c>
-      <c r="G43" s="4" t="n">
-        <v>7980</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>90</v>
+      <c r="G43" t="n">
+        <v>79800</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6230,33 +6230,33 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt — Remastered</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" t="n">
         <v>15893</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" t="n">
         <v>835349</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>27450</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>50</v>
+      <c r="G45" t="n">
+        <v>54900</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -6320,123 +6320,123 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="2" t="n">
         <v>8551</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="2" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="2" t="n">
         <v>295218</v>
       </c>
-      <c r="G48" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>75</v>
+      <c r="G48" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Indie, Simulation</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" t="n">
         <v>17281</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" t="n">
         <v>867404</v>
       </c>
-      <c r="G49" s="4" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>75</v>
+      <c r="G49" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="2" t="n">
         <v>14439</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="2" t="n">
         <v>94.3</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="2" t="n">
         <v>499828</v>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>28800</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>10</v>
+      <c r="G50" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Action, Indie, Early Access</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" t="n">
         <v>9978</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" t="n">
         <v>95.8</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" t="n">
         <v>768779</v>
       </c>
-      <c r="G51" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>30</v>
+      <c r="G51" t="n">
+        <v>21500</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6530,63 +6530,63 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Half-Life</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" t="n">
         <v>634</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" t="n">
         <v>96.5</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" t="n">
         <v>148221</v>
       </c>
-      <c r="G55" s="4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>80</v>
+      <c r="G55" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Monster Hunter: World</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="2" t="n">
         <v>11923</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="2" t="n">
         <v>493390</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>9570</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>74</v>
+      <c r="G56" s="2" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6650,33 +6650,33 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Project Zomboid</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Indie, RPG, Simulation, Early Access</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" t="n">
         <v>22864</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" t="n">
         <v>94.2</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" t="n">
         <v>377063</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>17750</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>33</v>
+      <c r="G59" t="n">
+        <v>26500</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6740,33 +6740,33 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Battlefield™ 2042</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Casual</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="2" t="n">
         <v>2774</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="2" t="n">
         <v>46.7</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="2" t="n">
         <v>297774</v>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>90</v>
+      <c r="G62" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6800,33 +6800,33 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Raft</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="2" t="n">
         <v>4701</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="2" t="n">
         <v>93.3</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="2" t="n">
         <v>346359</v>
       </c>
-      <c r="G64" s="4" t="n">
-        <v>14070</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>33</v>
+      <c r="G64" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -6890,93 +6890,93 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" t="n">
         <v>64</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Counter-Strike</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" t="n">
         <v>7323</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="F67" t="n">
         <v>250245</v>
       </c>
-      <c r="G67" s="4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>80</v>
+      <c r="G67" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Counter-Strike: Source</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="2" t="n">
         <v>6187</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="2" t="n">
         <v>96.3</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="2" t="n">
         <v>182234</v>
       </c>
-      <c r="G68" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>80</v>
+      <c r="G68" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" t="n">
         <v>66</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Schedule I</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Action, Indie, Simulation, Strategy, Early Access</t>
         </is>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" t="n">
         <v>22757</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" t="n">
         <v>204041</v>
       </c>
-      <c r="G69" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>30</v>
+      <c r="G69" t="n">
+        <v>21500</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -7010,33 +7010,33 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" t="n">
         <v>68</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" t="n">
         <v>638</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" t="n">
         <v>98.5</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" t="n">
         <v>177741</v>
       </c>
-      <c r="G71" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>80</v>
+      <c r="G71" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -7100,153 +7100,153 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="2" t="n">
         <v>30542</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="2" t="n">
         <v>95.3</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="2" t="n">
         <v>499061</v>
       </c>
-      <c r="G74" s="4" t="n">
-        <v>5270</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>66</v>
+      <c r="G74" s="2" t="n">
+        <v>15500</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" t="n">
         <v>72</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" t="n">
         <v>4953</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" t="n">
         <v>95.2</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" t="n">
         <v>457632</v>
       </c>
-      <c r="G75" s="4" t="n">
-        <v>2740</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>90</v>
+      <c r="G75" t="n">
+        <v>27400</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="2" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="2" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>6150</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>70</v>
+      <c r="G76" s="2" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" t="n">
         <v>17045</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" t="n">
         <v>370046</v>
       </c>
-      <c r="G77" s="4" t="n">
-        <v>25850</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>45</v>
+      <c r="G77" t="n">
+        <v>47000</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Counter-Strike: Condition Zero</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="2" t="n">
         <v>89.8</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="2" t="n">
         <v>14977</v>
       </c>
-      <c r="G78" s="4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>80</v>
+      <c r="G78" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -7340,33 +7340,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="2" t="n">
         <v>6300</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="2" t="n">
         <v>248220</v>
       </c>
-      <c r="G82" s="4" t="n">
-        <v>14680</v>
-      </c>
-      <c r="H82" s="4" t="n">
-        <v>60</v>
+      <c r="G82" s="2" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7400,243 +7400,243 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>CyberCorp</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="2" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="2" t="n">
         <v>322</v>
       </c>
-      <c r="G84" s="4" t="n">
-        <v>8250</v>
-      </c>
-      <c r="H84" s="4" t="n">
-        <v>50</v>
+      <c r="G84" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" t="n">
         <v>82</v>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Half-Life 2</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" t="n">
         <v>1555</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" t="n">
         <v>245627</v>
       </c>
-      <c r="G85" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H85" s="4" t="n">
-        <v>80</v>
+      <c r="G85" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Arma 3</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Action, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="2" t="n">
         <v>7181</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="2" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="2" t="n">
         <v>283264</v>
       </c>
-      <c r="G86" s="4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>75</v>
+      <c r="G86" s="2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Sons Of The Forest</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" t="n">
         <v>4450</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" t="n">
         <v>87.8</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" t="n">
         <v>253546</v>
       </c>
-      <c r="G87" s="4" t="n">
-        <v>9280</v>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>71</v>
+      <c r="G87" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Grim Dawn</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="2" t="n">
         <v>2376</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="2" t="n">
         <v>93.7</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="2" t="n">
         <v>99730</v>
       </c>
-      <c r="G88" s="4" t="n">
-        <v>3970</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>85</v>
+      <c r="G88" s="2" t="n">
+        <v>26500</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" t="n">
         <v>86</v>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Cities: Skylines</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" t="n">
         <v>8842</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" t="n">
         <v>93</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" t="n">
         <v>275770</v>
       </c>
-      <c r="G89" s="4" t="n">
-        <v>9900</v>
-      </c>
-      <c r="H89" s="4" t="n">
-        <v>70</v>
+      <c r="G89" t="n">
+        <v>33000</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Mount &amp; Blade II: Bannerlord</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Action, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="D90" s="2" t="n">
         <v>14477</v>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="2" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="2" t="n">
         <v>264391</v>
       </c>
-      <c r="G90" s="4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H90" s="4" t="n">
-        <v>50</v>
+      <c r="G90" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" t="n">
         <v>88</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Sid Meier's Civilization® V</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="D91" t="n">
         <v>12206</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" t="n">
         <v>95.8</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" t="n">
         <v>204265</v>
       </c>
-      <c r="G91" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>75</v>
+      <c r="G91" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7670,63 +7670,63 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" t="n">
         <v>90</v>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Sid Meier’s Civilization® VI</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="D93" t="n">
         <v>25420</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" t="n">
         <v>349920</v>
       </c>
-      <c r="G93" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="H93" s="4" t="n">
-        <v>90</v>
+      <c r="G93" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="2" t="n">
         <v>11179</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="2" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="2" t="n">
         <v>392287</v>
       </c>
-      <c r="G94" s="4" t="n">
-        <v>8800</v>
-      </c>
-      <c r="H94" s="4" t="n">
-        <v>60</v>
+      <c r="G94" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7760,153 +7760,153 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Warhammer 40,000: Rogue Trader</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Strategy</t>
         </is>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="D96" s="2" t="n">
         <v>3582</v>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="2" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="2" t="n">
         <v>30805</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>15900</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>70</v>
+      <c r="G96" s="2" t="n">
+        <v>53000</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" t="n">
         <v>94</v>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Battlefield™ V</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="D97" t="n">
         <v>6327</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" t="n">
         <v>250288</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>90</v>
+      <c r="G97" t="n">
+        <v>55000</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>R.E.P.O.</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Action, Early Access</t>
         </is>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="D98" s="2" t="n">
         <v>32349</v>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="2" t="n">
         <v>96.5</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="2" t="n">
         <v>185642</v>
       </c>
-      <c r="G98" s="4" t="n">
-        <v>6950</v>
-      </c>
-      <c r="H98" s="4" t="n">
-        <v>35</v>
+      <c r="G98" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" t="n">
         <v>96</v>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>DayZ</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Action, Adventure, Massively Multiplayer</t>
         </is>
       </c>
-      <c r="D99" s="4" t="n">
+      <c r="D99" t="n">
         <v>37066</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" t="n">
         <v>76.8</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" t="n">
         <v>430252</v>
       </c>
-      <c r="G99" s="4" t="n">
-        <v>29500</v>
-      </c>
-      <c r="H99" s="4" t="n">
-        <v>50</v>
+      <c r="G99" t="n">
+        <v>59000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Adventure, Indie, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="D100" s="2" t="n">
         <v>12596</v>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="2" t="n">
         <v>97.2</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="2" t="n">
         <v>232064</v>
       </c>
-      <c r="G100" s="4" t="n">
-        <v>29400</v>
-      </c>
-      <c r="H100" s="4" t="n">
-        <v>30</v>
+      <c r="G100" s="2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-08</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-08</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-08</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-09</t>
+          <t>Steam 인기 차트 — 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-09</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-09</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-09</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-10</t>
+          <t>Steam 인기 차트 — 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-10</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-10</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-10</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-11</t>
+          <t>Steam 인기 차트 — 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-11</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-11</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-11</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-12</t>
+          <t>Steam 인기 차트 — 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-12</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-12</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-12</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-13</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1975,10 +1975,10 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10700</v>
+        <v>5350</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>10700</v>
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2195,10 +2195,10 @@
         <v>713071</v>
       </c>
       <c r="J39" t="n">
-        <v>66000</v>
+        <v>19800</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L39" t="n">
         <v>66000</v>
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4527,10 +4527,10 @@
         <v>326054</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>22000</v>
+        <v>5500</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>22000</v>
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-13</t>
+          <t>Steam 인기 차트 — 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5960,33 +5960,33 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="4" t="n">
         <v>27254</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="4" t="n">
         <v>663082</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
+      <c r="G36" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -6110,33 +6110,33 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>22265</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="4" t="n">
         <v>844921</v>
       </c>
-      <c r="G41" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
+      <c r="G41" s="4" t="n">
+        <v>19800</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="42">
@@ -7700,33 +7700,33 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="4" t="n">
         <v>11179</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" s="4" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="4" t="n">
         <v>392287</v>
       </c>
-      <c r="G94" s="2" t="n">
-        <v>22000</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>0</v>
+      <c r="G94" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="95">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-13</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-13</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-13</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-14</t>
+          <t>Steam 인기 차트 — 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-14</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-14</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-14</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1319,10 +1319,10 @@
         <v>1373979</v>
       </c>
       <c r="J19" t="n">
-        <v>5500</v>
+        <v>11000</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>11000</v>
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2283,10 +2283,10 @@
         <v>289966</v>
       </c>
       <c r="J41" t="n">
-        <v>79800</v>
+        <v>7980</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L41" t="n">
         <v>79800</v>
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4043,10 +4043,10 @@
         <v>307041</v>
       </c>
       <c r="J81" t="n">
-        <v>37500</v>
+        <v>75000</v>
       </c>
       <c r="K81" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>75000</v>
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-15</t>
+          <t>Steam 인기 차트 — 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5514,33 +5514,33 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" t="n">
         <v>24580</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" t="n">
         <v>97.5</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" t="n">
         <v>1409473</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>50</v>
+      <c r="G21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -6170,33 +6170,33 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>5716</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>90.2</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="4" t="n">
         <v>321395</v>
       </c>
-      <c r="G43" t="n">
-        <v>79800</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
+      <c r="G43" s="4" t="n">
+        <v>7980</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="44">
@@ -7370,33 +7370,33 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" t="n">
         <v>80</v>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Sekiro™: Shadows Die Twice - GOTY Edition</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" t="n">
         <v>6767</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" t="n">
         <v>95.3</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" t="n">
         <v>322234</v>
       </c>
-      <c r="G83" s="4" t="n">
-        <v>37500</v>
-      </c>
-      <c r="H83" s="4" t="n">
-        <v>50</v>
+      <c r="G83" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-15</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-15</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-15</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-16</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-16</t>
+          <t>Steam 인기 차트 — 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-16</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-16</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-16</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-17</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-17</t>
+          <t>Steam 인기 차트 — 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-17</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-17</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-17</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-18</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-18</t>
+          <t>Steam 인기 차트 — 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-18</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-18</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-18</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2239,10 +2239,10 @@
         <v>630223</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21500</v>
+        <v>8600</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>21500</v>
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2635,10 +2635,10 @@
         <v>736611</v>
       </c>
       <c r="J49" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L49" t="n">
         <v>21500</v>
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-19</t>
+          <t>Steam 인기 차트 — 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6140,33 +6140,33 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="4" t="n">
         <v>44886</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="4" t="n">
         <v>797216</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>21500</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
+      <c r="G42" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -6410,33 +6410,33 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Action, Indie, Early Access</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>9978</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="4" t="n">
         <v>768779</v>
       </c>
-      <c r="G51" t="n">
-        <v>21500</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
+      <c r="G51" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-19</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-19</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-19</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-20</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-20</t>
+          <t>Steam 인기 차트 — 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-20</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-20</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-20</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-21</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1143,10 +1143,10 @@
         <v>127273</v>
       </c>
       <c r="J15" t="n">
-        <v>45800</v>
+        <v>34350</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
         <v>45800</v>
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-21</t>
+          <t>Steam 인기 차트 — 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5394,33 +5394,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="G17" t="n">
-        <v>45800</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+      <c r="G17" s="4" t="n">
+        <v>34350</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-21</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-21</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-21</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-22</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -705,10 +705,10 @@
         <v>358266</v>
       </c>
       <c r="J5" t="n">
-        <v>22400</v>
+        <v>32000</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>32000</v>
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2283,10 +2283,10 @@
         <v>289966</v>
       </c>
       <c r="J41" t="n">
-        <v>7980</v>
+        <v>79800</v>
       </c>
       <c r="K41" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>79800</v>
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2415,10 +2415,10 @@
         <v>643681</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>5500</v>
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3075,10 +3075,10 @@
         <v>676667</v>
       </c>
       <c r="J59" t="n">
-        <v>18250</v>
+        <v>73000</v>
       </c>
       <c r="K59" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>73000</v>
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3647,10 +3647,10 @@
         <v>475393</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15500</v>
+        <v>5270</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>15500</v>
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4879,10 +4879,10 @@
         <v>293127</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>8580</v>
+        <v>26000</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>26000</v>
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-22</t>
+          <t>Steam 인기 차트 — 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -5096,33 +5096,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>18028</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>380709</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>22400</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>30</v>
+      <c r="G7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6170,33 +6170,33 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" t="n">
         <v>5716</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" t="n">
         <v>90.2</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" t="n">
         <v>321395</v>
       </c>
-      <c r="G43" s="4" t="n">
-        <v>7980</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>90</v>
+      <c r="G43" t="n">
+        <v>79800</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6260,33 +6260,33 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Casual</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>3832</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="2" t="n">
         <v>700785</v>
       </c>
-      <c r="G46" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>40</v>
+      <c r="G46" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -6710,33 +6710,33 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Red Dead Redemption 2</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" t="n">
         <v>29885</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" t="n">
         <v>92.2</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" t="n">
         <v>733542</v>
       </c>
-      <c r="G61" s="4" t="n">
-        <v>18250</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>75</v>
+      <c r="G61" t="n">
+        <v>73000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -7100,33 +7100,33 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Don't Starve Together</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="4" t="n">
         <v>30542</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="4" t="n">
         <v>95.3</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="4" t="n">
         <v>499061</v>
       </c>
-      <c r="G74" s="2" t="n">
-        <v>15500</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>0</v>
+      <c r="G74" s="4" t="n">
+        <v>5270</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="75">
@@ -7940,33 +7940,33 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Risk of Rain 2</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Action, Indie</t>
         </is>
       </c>
-      <c r="D102" s="4" t="n">
+      <c r="D102" s="2" t="n">
         <v>7902</v>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="2" t="n">
         <v>93.5</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="2" t="n">
         <v>313577</v>
       </c>
-      <c r="G102" s="4" t="n">
-        <v>8580</v>
-      </c>
-      <c r="H102" s="4" t="n">
-        <v>67</v>
+      <c r="G102" s="2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-22</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-22</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-22</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-23</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4527,10 +4527,10 @@
         <v>326054</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>5500</v>
+        <v>22000</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>22000</v>
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-23</t>
+          <t>Steam 인기 차트 — 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -7700,33 +7700,33 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Fallout 4</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="2" t="n">
         <v>11179</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="2" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="2" t="n">
         <v>392287</v>
       </c>
-      <c r="G94" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="H94" s="4" t="n">
-        <v>75</v>
+      <c r="G94" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-23</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-23</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-23</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-24</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-24</t>
+          <t>Steam 인기 차트 — 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-24</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-24</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-24</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-25</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1757,10 +1757,10 @@
         <v>612177</v>
       </c>
       <c r="J29" t="n">
-        <v>16500</v>
+        <v>10890</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L29" t="n">
         <v>16500</v>
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-25</t>
+          <t>Steam 인기 차트 — 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5812,33 +5812,33 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>22170</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>83.8</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="4" t="n">
         <v>730170</v>
       </c>
-      <c r="G31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
+      <c r="G31" s="4" t="n">
+        <v>10890</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-25</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-25</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-25</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-26</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1669,10 +1669,10 @@
         <v>1071135</v>
       </c>
       <c r="J27" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" t="n">
         <v>42000</v>
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1845,10 +1845,10 @@
         <v>599805</v>
       </c>
       <c r="J31" t="n">
-        <v>20500</v>
+        <v>4100</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L31" t="n">
         <v>20500</v>
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2195,10 +2195,10 @@
         <v>713071</v>
       </c>
       <c r="J39" t="n">
-        <v>19800</v>
+        <v>66000</v>
       </c>
       <c r="K39" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>66000</v>
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3691,10 +3691,10 @@
         <v>435687</v>
       </c>
       <c r="J73" t="n">
-        <v>27400</v>
+        <v>2740</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L73" t="n">
         <v>27400</v>
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3779,10 +3779,10 @@
         <v>327889</v>
       </c>
       <c r="J75" t="n">
-        <v>47000</v>
+        <v>25850</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L75" t="n">
         <v>47000</v>
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3999,10 +3999,10 @@
         <v>181110</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36700</v>
+        <v>14680</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>36700</v>
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4219,10 +4219,10 @@
         <v>222495</v>
       </c>
       <c r="J85" t="n">
-        <v>32000</v>
+        <v>8960</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L85" t="n">
         <v>32000</v>
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4703,10 +4703,10 @@
         <v>179154</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>10700</v>
+        <v>6950</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>10700</v>
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4747,10 +4747,10 @@
         <v>330349</v>
       </c>
       <c r="J97" t="n">
-        <v>59000</v>
+        <v>29500</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L97" t="n">
         <v>59000</v>
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-26</t>
+          <t>Steam 인기 차트 — 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5752,33 +5752,33 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>143870</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>87.2</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="4" t="n">
         <v>1227784</v>
       </c>
-      <c r="G29" t="n">
-        <v>42000</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
+      <c r="G29" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -5872,33 +5872,33 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>2892</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>95.5</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="4" t="n">
         <v>627791</v>
       </c>
-      <c r="G33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
+      <c r="G33" s="4" t="n">
+        <v>4100</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -6110,33 +6110,33 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>RPG</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" t="n">
         <v>22265</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" t="n">
         <v>844921</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>19800</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>70</v>
+      <c r="G41" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -7130,33 +7130,33 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Dying Light</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>4953</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="4" t="n">
         <v>95.2</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="4" t="n">
         <v>457632</v>
       </c>
-      <c r="G75" t="n">
-        <v>27400</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
+      <c r="G75" s="4" t="n">
+        <v>2740</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="76">
@@ -7190,33 +7190,33 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>7 Days to Die</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, RPG, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>17045</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="4" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="4" t="n">
         <v>370046</v>
       </c>
-      <c r="G77" t="n">
-        <v>47000</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
+      <c r="G77" s="4" t="n">
+        <v>25850</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="78">
@@ -7340,33 +7340,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Hunt: Showdown 1896</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="4" t="n">
         <v>6300</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="4" t="n">
         <v>248220</v>
       </c>
-      <c r="G82" s="2" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>0</v>
+      <c r="G82" s="4" t="n">
+        <v>14680</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="83">
@@ -7490,33 +7490,33 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Sons Of The Forest</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>4450</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="4" t="n">
         <v>87.8</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="4" t="n">
         <v>253546</v>
       </c>
-      <c r="G87" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
+      <c r="G87" s="4" t="n">
+        <v>8960</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="88">
@@ -7820,63 +7820,63 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>R.E.P.O.</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Action, Early Access</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="4" t="n">
         <v>32349</v>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E98" s="4" t="n">
         <v>96.5</v>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="4" t="n">
         <v>185642</v>
       </c>
-      <c r="G98" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
+      <c r="G98" s="4" t="n">
+        <v>6950</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>DayZ</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>Action, Adventure, Massively Multiplayer</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>37066</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="4" t="n">
         <v>76.8</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="4" t="n">
         <v>430252</v>
       </c>
-      <c r="G99" t="n">
-        <v>59000</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
+      <c r="G99" s="4" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="100">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-26</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-26</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-26</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-27</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1975,10 +1975,10 @@
         <v>594327</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5350</v>
+        <v>10700</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>10700</v>
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-27</t>
+          <t>Steam 인기 차트 — 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -5960,33 +5960,33 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Action, RPG</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="2" t="n">
         <v>27254</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="2" t="n">
         <v>663082</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>5350</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>50</v>
+      <c r="G36" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-27</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-27</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-27</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-28</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-28</t>
+          <t>Steam 인기 차트 — 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-28</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-28</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-28</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-29</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3207,10 +3207,10 @@
         <v>323198</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21000</v>
+        <v>14070</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>21000</v>
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3735,10 +3735,10 @@
         <v>202253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>20500</v>
+        <v>6150</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>20500</v>
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-29</t>
+          <t>Steam 인기 차트 — 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6800,33 +6800,33 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Raft</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="4" t="n">
         <v>4701</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="4" t="n">
         <v>93.3</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="4" t="n">
         <v>346359</v>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>0</v>
+      <c r="G64" s="4" t="n">
+        <v>14070</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="65">
@@ -7160,33 +7160,33 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Human Fall Flat</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="4" t="n">
         <v>950</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="4" t="n">
         <v>94.7</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="4" t="n">
         <v>213640</v>
       </c>
-      <c r="G76" s="2" t="n">
-        <v>20500</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>0</v>
+      <c r="G76" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="77">
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-29</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-29</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-29</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-30</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,7 +585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -629,7 +629,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -805,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -849,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -893,7 +893,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1025,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1067,7 +1067,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1111,7 +1111,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1199,7 +1199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1243,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1287,7 +1287,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1331,7 +1331,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1461,7 +1461,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1505,7 +1505,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1549,7 +1549,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1593,7 +1593,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1637,7 +1637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1681,7 +1681,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1725,7 +1725,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1769,7 +1769,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1813,7 +1813,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1857,7 +1857,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1943,7 +1943,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1987,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2031,7 +2031,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2075,7 +2075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2119,7 +2119,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2163,7 +2163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2207,7 +2207,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2295,7 +2295,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2339,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2383,7 +2383,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2427,7 +2427,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2471,7 +2471,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2515,7 +2515,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2559,7 +2559,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2603,7 +2603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2647,7 +2647,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2691,7 +2691,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2779,7 +2779,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2823,7 +2823,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2867,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2911,7 +2911,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2955,7 +2955,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2999,7 +2999,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -3043,7 +3043,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3175,7 +3175,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3219,7 +3219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3263,7 +3263,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3307,7 +3307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3351,7 +3351,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3395,7 +3395,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3439,7 +3439,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3527,7 +3527,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3571,7 +3571,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3615,7 +3615,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3659,7 +3659,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3703,7 +3703,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3747,7 +3747,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3791,7 +3791,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3835,7 +3835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3879,7 +3879,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3923,7 +3923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3967,7 +3967,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -4011,7 +4011,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4055,7 +4055,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4143,7 +4143,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -4187,7 +4187,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4231,7 +4231,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -4275,7 +4275,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4319,7 +4319,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -4363,7 +4363,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4407,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -4451,7 +4451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4495,7 +4495,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -4539,7 +4539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4583,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4627,7 +4627,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,7 +4671,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4715,7 +4715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4759,7 +4759,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4803,7 +4803,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4847,7 +4847,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4891,7 +4891,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4959,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-10-30</t>
+          <t>Steam 인기 차트 — 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-30</t>
+          <t>1주(7일)+ 상위 100위 유지 게임 — 기준일: 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-30</t>
+          <t>2주(14일)+ 상위 100위 유지 게임 — 기준일: 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-30</t>
+          <t>4주(28일)+ 상위 100위 유지 게임 — 기준일: 2026-10-31</t>
         </is>
       </c>
     </row>
